--- a/artfynd/A 28823-2024 artfynd.xlsx
+++ b/artfynd/A 28823-2024 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121107064</v>
+        <v>121107051</v>
       </c>
       <c r="B6" t="n">
-        <v>74703</v>
+        <v>94484</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6486</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455767</v>
+        <v>455911</v>
       </c>
       <c r="R6" t="n">
-        <v>7037472</v>
+        <v>7037465</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,22 +1192,12 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På gammal gran, i hålighet vid basen # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1225,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107062</v>
+        <v>121107059</v>
       </c>
       <c r="B7" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,16 +1249,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455798</v>
+        <v>455892</v>
       </c>
       <c r="R7" t="n">
-        <v>7037492</v>
+        <v>7037497</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107065</v>
+        <v>121107066</v>
       </c>
       <c r="B8" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455770</v>
+        <v>455746</v>
       </c>
       <c r="R8" t="n">
-        <v>7037463</v>
+        <v>7037456</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,12 +1437,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Mycket rikligt, draperade träd</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121107060</v>
+        <v>121107052</v>
       </c>
       <c r="B9" t="n">
-        <v>78598</v>
+        <v>105171</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1506,25 +1501,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1534,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455889</v>
+        <v>455910</v>
       </c>
       <c r="R9" t="n">
-        <v>7037501</v>
+        <v>7037468</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1569,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,12 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,22 +1588,12 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1631,10 +1611,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121107058</v>
+        <v>121107061</v>
       </c>
       <c r="B10" t="n">
-        <v>74705</v>
+        <v>78601</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,21 +1627,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1671,10 +1651,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455915</v>
+        <v>455871</v>
       </c>
       <c r="R10" t="n">
-        <v>7037497</v>
+        <v>7037484</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,7 +1696,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1763,10 +1748,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121107066</v>
+        <v>121107062</v>
       </c>
       <c r="B11" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1803,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455746</v>
+        <v>455798</v>
       </c>
       <c r="R11" t="n">
-        <v>7037456</v>
+        <v>7037492</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1838,7 +1823,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1848,12 +1833,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Mycket rikligt, draperade träd</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1900,10 +1880,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121107056</v>
+        <v>121107064</v>
       </c>
       <c r="B12" t="n">
-        <v>74703</v>
+        <v>74706</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1940,10 +1920,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455917</v>
+        <v>455767</v>
       </c>
       <c r="R12" t="n">
-        <v>7037493</v>
+        <v>7037472</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1975,7 +1955,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1985,7 +1965,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1999,7 +1979,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2014,7 +1994,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+          <t>På gammal gran, i hålighet vid basen # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2032,10 +2012,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121107061</v>
+        <v>121107065</v>
       </c>
       <c r="B13" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2072,10 +2052,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455871</v>
+        <v>455770</v>
       </c>
       <c r="R13" t="n">
-        <v>7037484</v>
+        <v>7037463</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2107,7 +2087,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2117,7 +2097,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -2172,7 +2152,7 @@
         <v>121107055</v>
       </c>
       <c r="B14" t="n">
-        <v>82382</v>
+        <v>82385</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2301,10 +2281,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121107051</v>
+        <v>121107058</v>
       </c>
       <c r="B15" t="n">
-        <v>94474</v>
+        <v>74708</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2313,25 +2293,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2341,10 +2321,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455911</v>
+        <v>455915</v>
       </c>
       <c r="R15" t="n">
-        <v>7037465</v>
+        <v>7037497</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2376,7 +2356,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2386,7 +2366,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2400,12 +2380,22 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2426,7 +2416,7 @@
         <v>121107057</v>
       </c>
       <c r="B16" t="n">
-        <v>74710</v>
+        <v>74713</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2555,10 +2545,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121107059</v>
+        <v>121107056</v>
       </c>
       <c r="B17" t="n">
-        <v>78598</v>
+        <v>74706</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2567,43 +2557,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455892</v>
+        <v>455917</v>
       </c>
       <c r="R17" t="n">
-        <v>7037497</v>
+        <v>7037493</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2635,7 +2620,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2645,7 +2630,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2659,7 +2644,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -2674,7 +2659,7 @@
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2692,10 +2677,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121107049</v>
+        <v>121107060</v>
       </c>
       <c r="B18" t="n">
-        <v>91620</v>
+        <v>78601</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2704,25 +2689,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2732,10 +2717,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455920</v>
+        <v>455889</v>
       </c>
       <c r="R18" t="n">
-        <v>7037457</v>
+        <v>7037501</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2767,7 +2752,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2777,7 +2762,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2791,12 +2781,22 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2814,10 +2814,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121107052</v>
+        <v>121107049</v>
       </c>
       <c r="B19" t="n">
-        <v>105161</v>
+        <v>91630</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221725</v>
+        <v>4769</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455910</v>
+        <v>455920</v>
       </c>
       <c r="R19" t="n">
-        <v>7037468</v>
+        <v>7037457</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2939,7 +2939,7 @@
         <v>120752466</v>
       </c>
       <c r="B20" t="n">
-        <v>74703</v>
+        <v>74706</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>120752465</v>
       </c>
       <c r="B21" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 28823-2024 artfynd.xlsx
+++ b/artfynd/A 28823-2024 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121107051</v>
+        <v>121107052</v>
       </c>
       <c r="B6" t="n">
-        <v>94484</v>
+        <v>105171</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>221725</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455911</v>
+        <v>455910</v>
       </c>
       <c r="R6" t="n">
-        <v>7037465</v>
+        <v>7037468</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107059</v>
+        <v>121107060</v>
       </c>
       <c r="B7" t="n">
         <v>78601</v>
@@ -1249,21 +1249,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455892</v>
+        <v>455889</v>
       </c>
       <c r="R7" t="n">
-        <v>7037497</v>
+        <v>7037501</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1300,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107066</v>
+        <v>121107059</v>
       </c>
       <c r="B8" t="n">
         <v>78601</v>
@@ -1386,16 +1386,21 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455746</v>
+        <v>455892</v>
       </c>
       <c r="R8" t="n">
-        <v>7037456</v>
+        <v>7037497</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,12 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Mycket rikligt, draperade träd</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121107052</v>
+        <v>121107058</v>
       </c>
       <c r="B9" t="n">
-        <v>105171</v>
+        <v>74708</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,25 +1501,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221725</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1529,10 +1529,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455910</v>
+        <v>455915</v>
       </c>
       <c r="R9" t="n">
-        <v>7037468</v>
+        <v>7037497</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,12 +1588,22 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1611,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121107061</v>
+        <v>121107055</v>
       </c>
       <c r="B10" t="n">
-        <v>78601</v>
+        <v>82385</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1627,21 +1637,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1651,10 +1661,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455871</v>
+        <v>455914</v>
       </c>
       <c r="R10" t="n">
-        <v>7037484</v>
+        <v>7037492</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1696,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,12 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,7 +1720,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1730,7 +1735,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1748,7 +1753,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121107062</v>
+        <v>121107066</v>
       </c>
       <c r="B11" t="n">
         <v>78601</v>
@@ -1788,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455798</v>
+        <v>455746</v>
       </c>
       <c r="R11" t="n">
-        <v>7037492</v>
+        <v>7037456</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1823,7 +1828,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1833,7 +1838,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Mycket rikligt, draperade träd</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1880,7 +1890,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121107064</v>
+        <v>121107056</v>
       </c>
       <c r="B12" t="n">
         <v>74706</v>
@@ -1920,10 +1930,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455767</v>
+        <v>455917</v>
       </c>
       <c r="R12" t="n">
-        <v>7037472</v>
+        <v>7037493</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1955,7 +1965,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1965,7 +1975,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1979,7 +1989,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -1994,7 +2004,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>På gammal gran, i hålighet vid basen # Picea abies</t>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2012,10 +2022,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121107065</v>
+        <v>121107064</v>
       </c>
       <c r="B13" t="n">
-        <v>78601</v>
+        <v>74706</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2024,25 +2034,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2052,10 +2062,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455770</v>
+        <v>455767</v>
       </c>
       <c r="R13" t="n">
-        <v>7037463</v>
+        <v>7037472</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2087,7 +2097,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2097,12 +2107,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2131,7 +2136,7 @@
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>På gammal gran, i hålighet vid basen # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2149,10 +2154,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121107055</v>
+        <v>121107062</v>
       </c>
       <c r="B14" t="n">
-        <v>82385</v>
+        <v>78601</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2165,21 +2170,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2189,7 +2194,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455914</v>
+        <v>455798</v>
       </c>
       <c r="R14" t="n">
         <v>7037492</v>
@@ -2224,7 +2229,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2234,7 +2239,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2248,7 +2253,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2263,7 +2268,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2281,10 +2286,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121107058</v>
+        <v>121107061</v>
       </c>
       <c r="B15" t="n">
-        <v>74708</v>
+        <v>78601</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2297,21 +2302,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2321,10 +2326,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455915</v>
+        <v>455871</v>
       </c>
       <c r="R15" t="n">
-        <v>7037497</v>
+        <v>7037484</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2356,7 +2361,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2366,7 +2371,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2413,10 +2423,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121107057</v>
+        <v>121107049</v>
       </c>
       <c r="B16" t="n">
-        <v>74713</v>
+        <v>91630</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2425,25 +2435,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1467</v>
+        <v>4769</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2453,10 +2463,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455917</v>
+        <v>455920</v>
       </c>
       <c r="R16" t="n">
-        <v>7037493</v>
+        <v>7037457</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2488,7 +2498,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2498,7 +2508,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2515,19 +2525,9 @@
           <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2545,10 +2545,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121107056</v>
+        <v>121107051</v>
       </c>
       <c r="B17" t="n">
-        <v>74706</v>
+        <v>94484</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2557,25 +2557,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6486</v>
+        <v>2809</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455917</v>
+        <v>455911</v>
       </c>
       <c r="R17" t="n">
-        <v>7037493</v>
+        <v>7037465</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2647,19 +2647,9 @@
           <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2677,7 +2667,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121107060</v>
+        <v>121107065</v>
       </c>
       <c r="B18" t="n">
         <v>78601</v>
@@ -2717,10 +2707,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455889</v>
+        <v>455770</v>
       </c>
       <c r="R18" t="n">
-        <v>7037501</v>
+        <v>7037463</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2752,7 +2742,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2762,7 +2752,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2814,10 +2804,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121107049</v>
+        <v>121107057</v>
       </c>
       <c r="B19" t="n">
-        <v>91630</v>
+        <v>74713</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2826,25 +2816,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4769</v>
+        <v>1467</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2854,10 +2844,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455920</v>
+        <v>455917</v>
       </c>
       <c r="R19" t="n">
-        <v>7037457</v>
+        <v>7037493</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2889,7 +2879,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2899,7 +2889,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2916,9 +2906,19 @@
           <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120752466</v>
+        <v>120752465</v>
       </c>
       <c r="B20" t="n">
-        <v>74706</v>
+        <v>78601</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2948,41 +2948,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>MD3:Krokom, SE-JA, SE, Jmt</t>
+          <t>MD4:Krokom, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455918</v>
+        <v>455887</v>
       </c>
       <c r="R20" t="n">
-        <v>7037497</v>
+        <v>7037494</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3048,10 +3048,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120752465</v>
+        <v>120752466</v>
       </c>
       <c r="B21" t="n">
-        <v>78601</v>
+        <v>74706</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3060,41 +3060,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>MD4:Krokom, SE-JA, SE, Jmt</t>
+          <t>MD3:Krokom, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455887</v>
+        <v>455918</v>
       </c>
       <c r="R21" t="n">
-        <v>7037494</v>
+        <v>7037497</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 28823-2024 artfynd.xlsx
+++ b/artfynd/A 28823-2024 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121107052</v>
+        <v>121107057</v>
       </c>
       <c r="B6" t="n">
-        <v>105171</v>
+        <v>74715</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221725</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455910</v>
+        <v>455917</v>
       </c>
       <c r="R6" t="n">
-        <v>7037468</v>
+        <v>7037493</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,9 +1195,19 @@
           <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1215,10 +1225,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107060</v>
+        <v>121107064</v>
       </c>
       <c r="B7" t="n">
-        <v>78601</v>
+        <v>74708</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,25 +1237,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455889</v>
+        <v>455767</v>
       </c>
       <c r="R7" t="n">
-        <v>7037501</v>
+        <v>7037472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,12 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,7 +1339,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>På gammal gran, i hålighet vid basen # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1352,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107059</v>
+        <v>121107065</v>
       </c>
       <c r="B8" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,21 +1391,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455892</v>
+        <v>455770</v>
       </c>
       <c r="R8" t="n">
-        <v>7037497</v>
+        <v>7037463</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,10 +1494,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121107058</v>
+        <v>121107059</v>
       </c>
       <c r="B9" t="n">
-        <v>74708</v>
+        <v>78604</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1505,31 +1510,36 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455915</v>
+        <v>455892</v>
       </c>
       <c r="R9" t="n">
         <v>7037497</v>
@@ -1564,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,10 +1631,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121107055</v>
+        <v>121107062</v>
       </c>
       <c r="B10" t="n">
-        <v>82385</v>
+        <v>78604</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1637,21 +1647,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1661,7 +1671,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455914</v>
+        <v>455798</v>
       </c>
       <c r="R10" t="n">
         <v>7037492</v>
@@ -1696,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1706,7 +1716,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,7 +1730,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1735,7 +1745,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1753,10 +1763,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121107066</v>
+        <v>121107049</v>
       </c>
       <c r="B11" t="n">
-        <v>78601</v>
+        <v>91642</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1765,25 +1775,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1793,10 +1803,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455746</v>
+        <v>455920</v>
       </c>
       <c r="R11" t="n">
-        <v>7037456</v>
+        <v>7037457</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1828,7 +1838,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1838,12 +1848,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Mycket rikligt, draperade träd</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,22 +1862,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1890,10 +1885,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121107056</v>
+        <v>121107051</v>
       </c>
       <c r="B12" t="n">
-        <v>74706</v>
+        <v>94496</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1902,25 +1897,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6486</v>
+        <v>2809</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1930,10 +1925,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455917</v>
+        <v>455911</v>
       </c>
       <c r="R12" t="n">
-        <v>7037493</v>
+        <v>7037465</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1965,7 +1960,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1975,7 +1970,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1992,19 +1987,9 @@
           <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2022,10 +2007,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121107064</v>
+        <v>121107052</v>
       </c>
       <c r="B13" t="n">
-        <v>74706</v>
+        <v>105184</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2034,25 +2019,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6486</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2062,10 +2047,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455767</v>
+        <v>455910</v>
       </c>
       <c r="R13" t="n">
-        <v>7037472</v>
+        <v>7037468</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2097,7 +2082,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2107,7 +2092,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2121,22 +2106,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>På gammal gran, i hålighet vid basen # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2154,10 +2129,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121107062</v>
+        <v>121107056</v>
       </c>
       <c r="B14" t="n">
-        <v>78601</v>
+        <v>74708</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2166,25 +2141,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2194,10 +2169,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455798</v>
+        <v>455917</v>
       </c>
       <c r="R14" t="n">
-        <v>7037492</v>
+        <v>7037493</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2229,7 +2204,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2239,7 +2214,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2253,7 +2228,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2268,7 +2243,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2289,7 +2264,7 @@
         <v>121107061</v>
       </c>
       <c r="B15" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2423,10 +2398,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121107049</v>
+        <v>121107066</v>
       </c>
       <c r="B16" t="n">
-        <v>91630</v>
+        <v>78604</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2435,25 +2410,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2463,10 +2438,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455920</v>
+        <v>455746</v>
       </c>
       <c r="R16" t="n">
-        <v>7037457</v>
+        <v>7037456</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2498,7 +2473,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2508,7 +2483,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Mycket rikligt, draperade träd</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2522,12 +2502,22 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2545,10 +2535,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121107051</v>
+        <v>121107060</v>
       </c>
       <c r="B17" t="n">
-        <v>94484</v>
+        <v>78604</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2557,25 +2547,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2585,10 +2575,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455911</v>
+        <v>455889</v>
       </c>
       <c r="R17" t="n">
-        <v>7037465</v>
+        <v>7037501</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2620,7 +2610,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2630,7 +2620,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2644,12 +2639,22 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2667,10 +2672,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121107065</v>
+        <v>121107055</v>
       </c>
       <c r="B18" t="n">
-        <v>78601</v>
+        <v>82388</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2683,21 +2688,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2707,10 +2712,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455770</v>
+        <v>455914</v>
       </c>
       <c r="R18" t="n">
-        <v>7037463</v>
+        <v>7037492</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2742,7 +2747,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2752,12 +2757,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2804,10 +2804,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121107057</v>
+        <v>121107058</v>
       </c>
       <c r="B19" t="n">
-        <v>74713</v>
+        <v>74710</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2820,21 +2820,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1467</v>
+        <v>6440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455917</v>
+        <v>455915</v>
       </c>
       <c r="R19" t="n">
-        <v>7037493</v>
+        <v>7037497</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2889,7 +2889,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120752465</v>
+        <v>120752466</v>
       </c>
       <c r="B20" t="n">
-        <v>78601</v>
+        <v>74708</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2948,41 +2948,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>MD4:Krokom, SE-JA, SE, Jmt</t>
+          <t>MD3:Krokom, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455887</v>
+        <v>455918</v>
       </c>
       <c r="R20" t="n">
-        <v>7037494</v>
+        <v>7037497</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3048,10 +3048,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120752466</v>
+        <v>120752465</v>
       </c>
       <c r="B21" t="n">
-        <v>74706</v>
+        <v>78604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3060,41 +3060,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>MD3:Krokom, SE-JA, SE, Jmt</t>
+          <t>MD4:Krokom, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455918</v>
+        <v>455887</v>
       </c>
       <c r="R21" t="n">
-        <v>7037497</v>
+        <v>7037494</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 28823-2024 artfynd.xlsx
+++ b/artfynd/A 28823-2024 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121107057</v>
+        <v>121107049</v>
       </c>
       <c r="B6" t="n">
-        <v>74715</v>
+        <v>91643</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1467</v>
+        <v>4769</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455917</v>
+        <v>455920</v>
       </c>
       <c r="R6" t="n">
-        <v>7037493</v>
+        <v>7037457</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,19 +1195,9 @@
           <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1218,17 +1208,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107064</v>
+        <v>121107051</v>
       </c>
       <c r="B7" t="n">
-        <v>74708</v>
+        <v>94497</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1237,25 +1227,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6486</v>
+        <v>2809</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455767</v>
+        <v>455911</v>
       </c>
       <c r="R7" t="n">
-        <v>7037472</v>
+        <v>7037465</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,22 +1314,12 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På gammal gran, i hålighet vid basen # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1350,7 +1330,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1487,17 +1467,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121107059</v>
+        <v>121107055</v>
       </c>
       <c r="B9" t="n">
-        <v>78604</v>
+        <v>82388</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,39 +1490,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455892</v>
+        <v>455914</v>
       </c>
       <c r="R9" t="n">
-        <v>7037497</v>
+        <v>7037492</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1574,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,7 +1573,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1613,7 +1588,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1624,14 +1599,14 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121107062</v>
+        <v>121107059</v>
       </c>
       <c r="B10" t="n">
         <v>78604</v>
@@ -1665,16 +1640,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455798</v>
+        <v>455892</v>
       </c>
       <c r="R10" t="n">
-        <v>7037492</v>
+        <v>7037497</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,7 +1696,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1756,17 +1736,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121107049</v>
+        <v>121107061</v>
       </c>
       <c r="B11" t="n">
-        <v>91642</v>
+        <v>78604</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1775,25 +1755,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1803,10 +1783,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455920</v>
+        <v>455871</v>
       </c>
       <c r="R11" t="n">
-        <v>7037457</v>
+        <v>7037484</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1838,7 +1818,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1848,7 +1828,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,12 +1847,22 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1878,17 +1873,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121107051</v>
+        <v>121107062</v>
       </c>
       <c r="B12" t="n">
-        <v>94496</v>
+        <v>78604</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1897,25 +1892,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1925,10 +1920,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455911</v>
+        <v>455798</v>
       </c>
       <c r="R12" t="n">
-        <v>7037465</v>
+        <v>7037492</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1960,7 +1955,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1970,7 +1965,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,12 +1979,22 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2000,17 +2005,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121107052</v>
+        <v>121107056</v>
       </c>
       <c r="B13" t="n">
-        <v>105184</v>
+        <v>74708</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2019,25 +2024,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>6486</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2047,10 +2052,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455910</v>
+        <v>455917</v>
       </c>
       <c r="R13" t="n">
-        <v>7037468</v>
+        <v>7037493</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2082,7 +2087,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2092,7 +2097,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2109,9 +2114,19 @@
           <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2122,17 +2137,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121107056</v>
+        <v>121107066</v>
       </c>
       <c r="B14" t="n">
-        <v>74708</v>
+        <v>78604</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2141,25 +2156,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2169,10 +2184,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455917</v>
+        <v>455746</v>
       </c>
       <c r="R14" t="n">
-        <v>7037493</v>
+        <v>7037456</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2204,7 +2219,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2214,7 +2229,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Mycket rikligt, draperade träd</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2228,7 +2248,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2243,7 +2263,7 @@
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2254,14 +2274,14 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121107061</v>
+        <v>121107060</v>
       </c>
       <c r="B15" t="n">
         <v>78604</v>
@@ -2301,10 +2321,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455871</v>
+        <v>455889</v>
       </c>
       <c r="R15" t="n">
-        <v>7037484</v>
+        <v>7037501</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2336,7 +2356,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2346,7 +2366,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2391,17 +2411,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121107066</v>
+        <v>121107057</v>
       </c>
       <c r="B16" t="n">
-        <v>78604</v>
+        <v>74715</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2414,21 +2434,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2438,10 +2458,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455746</v>
+        <v>455917</v>
       </c>
       <c r="R16" t="n">
-        <v>7037456</v>
+        <v>7037493</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2473,7 +2493,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2483,12 +2503,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Mycket rikligt, draperade träd</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2502,7 +2517,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2517,7 +2532,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2528,17 +2543,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121107060</v>
+        <v>121107052</v>
       </c>
       <c r="B17" t="n">
-        <v>78604</v>
+        <v>105185</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2547,25 +2562,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2575,10 +2590,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455889</v>
+        <v>455910</v>
       </c>
       <c r="R17" t="n">
-        <v>7037501</v>
+        <v>7037468</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2610,7 +2625,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2620,12 +2635,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2639,22 +2649,12 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2665,17 +2665,17 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121107055</v>
+        <v>121107064</v>
       </c>
       <c r="B18" t="n">
-        <v>82388</v>
+        <v>74708</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2684,25 +2684,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6486</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2712,10 +2712,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455914</v>
+        <v>455767</v>
       </c>
       <c r="R18" t="n">
-        <v>7037492</v>
+        <v>7037472</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På gammal gran, i hålighet vid basen # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 28823-2024 artfynd.xlsx
+++ b/artfynd/A 28823-2024 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121107049</v>
+        <v>121107051</v>
       </c>
       <c r="B6" t="n">
-        <v>91643</v>
+        <v>94500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455920</v>
+        <v>455911</v>
       </c>
       <c r="R6" t="n">
-        <v>7037457</v>
+        <v>7037465</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1208,17 +1208,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107051</v>
+        <v>121107059</v>
       </c>
       <c r="B7" t="n">
-        <v>94497</v>
+        <v>78607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1227,38 +1227,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2809</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455911</v>
+        <v>455892</v>
       </c>
       <c r="R7" t="n">
-        <v>7037465</v>
+        <v>7037497</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1290,7 +1295,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1305,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,12 +1319,22 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1330,17 +1345,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107065</v>
+        <v>121107049</v>
       </c>
       <c r="B8" t="n">
-        <v>78604</v>
+        <v>91646</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1349,25 +1364,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1377,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455770</v>
+        <v>455920</v>
       </c>
       <c r="R8" t="n">
-        <v>7037463</v>
+        <v>7037457</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1422,12 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,22 +1451,12 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1467,17 +1467,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121107055</v>
+        <v>121107057</v>
       </c>
       <c r="B9" t="n">
-        <v>82388</v>
+        <v>74718</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,21 +1490,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1312</v>
+        <v>1467</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455914</v>
+        <v>455917</v>
       </c>
       <c r="R9" t="n">
-        <v>7037492</v>
+        <v>7037493</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1599,17 +1599,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121107059</v>
+        <v>121107060</v>
       </c>
       <c r="B10" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,21 +1640,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455892</v>
+        <v>455889</v>
       </c>
       <c r="R10" t="n">
-        <v>7037497</v>
+        <v>7037501</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1686,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1696,7 +1691,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1736,17 +1736,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121107061</v>
+        <v>121107055</v>
       </c>
       <c r="B11" t="n">
-        <v>78604</v>
+        <v>82391</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,21 +1759,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455871</v>
+        <v>455914</v>
       </c>
       <c r="R11" t="n">
-        <v>7037484</v>
+        <v>7037492</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1828,12 +1828,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,7 +1842,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1862,7 +1857,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1873,17 +1868,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121107062</v>
+        <v>121107058</v>
       </c>
       <c r="B12" t="n">
-        <v>78604</v>
+        <v>74713</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1896,21 +1891,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1920,10 +1915,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455798</v>
+        <v>455915</v>
       </c>
       <c r="R12" t="n">
-        <v>7037492</v>
+        <v>7037497</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1955,7 +1950,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1965,7 +1960,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2005,7 +2000,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2015,7 +2010,7 @@
         <v>121107056</v>
       </c>
       <c r="B13" t="n">
-        <v>74708</v>
+        <v>74711</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2137,7 +2132,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2147,7 +2142,7 @@
         <v>121107066</v>
       </c>
       <c r="B14" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2274,17 +2269,17 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121107060</v>
+        <v>121107062</v>
       </c>
       <c r="B15" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2321,10 +2316,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455889</v>
+        <v>455798</v>
       </c>
       <c r="R15" t="n">
-        <v>7037501</v>
+        <v>7037492</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2356,7 +2351,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2366,12 +2361,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2411,17 +2401,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121107057</v>
+        <v>121107065</v>
       </c>
       <c r="B16" t="n">
-        <v>74715</v>
+        <v>78607</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2434,21 +2424,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2458,10 +2448,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455917</v>
+        <v>455770</v>
       </c>
       <c r="R16" t="n">
-        <v>7037493</v>
+        <v>7037463</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2493,7 +2483,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2503,7 +2493,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2517,7 +2512,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2532,7 +2527,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2543,17 +2538,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121107052</v>
+        <v>121107061</v>
       </c>
       <c r="B17" t="n">
-        <v>105185</v>
+        <v>78607</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2562,25 +2557,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2590,10 +2585,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455910</v>
+        <v>455871</v>
       </c>
       <c r="R17" t="n">
-        <v>7037468</v>
+        <v>7037484</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2625,7 +2620,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2635,7 +2630,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2649,12 +2649,22 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2665,7 +2675,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2675,7 +2685,7 @@
         <v>121107064</v>
       </c>
       <c r="B18" t="n">
-        <v>74708</v>
+        <v>74711</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2797,17 +2807,17 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121107058</v>
+        <v>121107052</v>
       </c>
       <c r="B19" t="n">
-        <v>74710</v>
+        <v>105188</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2816,25 +2826,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6440</v>
+        <v>221725</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2844,10 +2854,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455915</v>
+        <v>455910</v>
       </c>
       <c r="R19" t="n">
-        <v>7037497</v>
+        <v>7037468</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2879,7 +2889,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2889,7 +2899,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2903,22 +2913,12 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2929,7 +2929,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist, Ludvig Nordin, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2939,7 +2939,7 @@
         <v>120752466</v>
       </c>
       <c r="B20" t="n">
-        <v>74708</v>
+        <v>74711</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>120752465</v>
       </c>
       <c r="B21" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>

--- a/artfynd/A 28823-2024 artfynd.xlsx
+++ b/artfynd/A 28823-2024 artfynd.xlsx
@@ -1093,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121107051</v>
+        <v>121107064</v>
       </c>
       <c r="B6" t="n">
-        <v>94500</v>
+        <v>74711</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,25 +1105,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2809</v>
+        <v>6486</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455911</v>
+        <v>455767</v>
       </c>
       <c r="R6" t="n">
-        <v>7037465</v>
+        <v>7037472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,12 +1192,22 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gammal gran, i hålighet vid basen # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1215,7 +1225,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107059</v>
+        <v>121107060</v>
       </c>
       <c r="B7" t="n">
         <v>78607</v>
@@ -1249,21 +1259,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455892</v>
+        <v>455889</v>
       </c>
       <c r="R7" t="n">
-        <v>7037497</v>
+        <v>7037501</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1305,7 +1310,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107049</v>
+        <v>121107052</v>
       </c>
       <c r="B8" t="n">
-        <v>91646</v>
+        <v>105188</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4769</v>
+        <v>221725</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455920</v>
+        <v>455910</v>
       </c>
       <c r="R8" t="n">
-        <v>7037457</v>
+        <v>7037468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1427,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121107057</v>
+        <v>121107065</v>
       </c>
       <c r="B9" t="n">
-        <v>74718</v>
+        <v>78607</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,21 +1500,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1467</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455917</v>
+        <v>455770</v>
       </c>
       <c r="R9" t="n">
-        <v>7037493</v>
+        <v>7037463</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1569,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:56</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1573,7 +1588,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -1588,7 +1603,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1606,10 +1621,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121107060</v>
+        <v>121107057</v>
       </c>
       <c r="B10" t="n">
-        <v>78607</v>
+        <v>74718</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,21 +1637,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1646,10 +1661,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455889</v>
+        <v>455917</v>
       </c>
       <c r="R10" t="n">
-        <v>7037501</v>
+        <v>7037493</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1681,7 +1696,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,12 +1706,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,7 +1720,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -1725,7 +1735,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1743,10 +1753,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121107055</v>
+        <v>121107061</v>
       </c>
       <c r="B11" t="n">
-        <v>82391</v>
+        <v>78607</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1759,21 +1769,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1783,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455914</v>
+        <v>455871</v>
       </c>
       <c r="R11" t="n">
-        <v>7037492</v>
+        <v>7037484</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1818,7 +1828,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1828,7 +1838,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,7 +1857,7 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1857,7 +1872,7 @@
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2007,10 +2022,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121107056</v>
+        <v>121107051</v>
       </c>
       <c r="B13" t="n">
-        <v>74711</v>
+        <v>94500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2019,25 +2034,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6486</v>
+        <v>2809</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2047,10 +2062,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455917</v>
+        <v>455911</v>
       </c>
       <c r="R13" t="n">
-        <v>7037493</v>
+        <v>7037465</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2082,7 +2097,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2092,7 +2107,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2109,19 +2124,9 @@
           <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2139,10 +2144,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121107066</v>
+        <v>121107049</v>
       </c>
       <c r="B14" t="n">
-        <v>78607</v>
+        <v>91646</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2151,25 +2156,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2179,10 +2184,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455746</v>
+        <v>455920</v>
       </c>
       <c r="R14" t="n">
-        <v>7037456</v>
+        <v>7037457</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2214,7 +2219,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2224,12 +2229,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Mycket rikligt, draperade träd</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2243,22 +2243,12 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2276,10 +2266,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121107062</v>
+        <v>121107055</v>
       </c>
       <c r="B15" t="n">
-        <v>78607</v>
+        <v>82391</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2292,21 +2282,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2316,7 +2306,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455798</v>
+        <v>455914</v>
       </c>
       <c r="R15" t="n">
         <v>7037492</v>
@@ -2351,7 +2341,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2361,7 +2351,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2375,7 +2365,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2390,7 +2380,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2408,10 +2398,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121107065</v>
+        <v>121107056</v>
       </c>
       <c r="B16" t="n">
-        <v>78607</v>
+        <v>74711</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2420,25 +2410,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2448,10 +2438,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455770</v>
+        <v>455917</v>
       </c>
       <c r="R16" t="n">
-        <v>7037463</v>
+        <v>7037493</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2483,7 +2473,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2493,12 +2483,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:56</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2512,7 +2497,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2527,7 +2512,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2545,7 +2530,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121107061</v>
+        <v>121107059</v>
       </c>
       <c r="B17" t="n">
         <v>78607</v>
@@ -2579,16 +2564,21 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455871</v>
+        <v>455892</v>
       </c>
       <c r="R17" t="n">
-        <v>7037484</v>
+        <v>7037497</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2620,7 +2610,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2630,12 +2620,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2682,10 +2667,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121107064</v>
+        <v>121107062</v>
       </c>
       <c r="B18" t="n">
-        <v>74711</v>
+        <v>78607</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2694,25 +2679,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2722,10 +2707,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>455767</v>
+        <v>455798</v>
       </c>
       <c r="R18" t="n">
-        <v>7037472</v>
+        <v>7037492</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2757,7 +2742,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2767,7 +2752,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2796,7 +2781,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>På gammal gran, i hålighet vid basen # Picea abies</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2814,10 +2799,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121107052</v>
+        <v>121107066</v>
       </c>
       <c r="B19" t="n">
-        <v>105188</v>
+        <v>78607</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2826,25 +2811,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2854,10 +2839,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455910</v>
+        <v>455746</v>
       </c>
       <c r="R19" t="n">
-        <v>7037468</v>
+        <v>7037456</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2889,7 +2874,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2899,7 +2884,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Mycket rikligt, draperade träd</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2913,12 +2903,22 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>

--- a/artfynd/A 28823-2024 artfynd.xlsx
+++ b/artfynd/A 28823-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3158,6 +3158,3729 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>121601584</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>455813</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7037433</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt på glasbjörk i gammal granskog, längsta bål 40 cm</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>121601174</v>
+      </c>
+      <c r="B23" t="n">
+        <v>74715</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Kläppberget, Kläppberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>455933</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7037605</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>121601908</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>455848</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7037606</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På gammal grov gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121598835</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78865</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6459</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Barkkornlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lopadium disciforme</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>455963</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7037616</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På gren på gammal gran</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121598520</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kläppberget, Kläppberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>455831</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7037676</v>
+      </c>
+      <c r="S26" t="n">
+        <v>8</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin, August Nordin</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>121599010</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>455998</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7037645</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>13:38</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På gammal gran, mer än 200 bålar, granen 55 cm dbh.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>121598559</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79079</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1797</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mjölig dropplav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Cliostomum leprosum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>455834</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7037660</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>121601299</v>
+      </c>
+      <c r="B29" t="n">
+        <v>90720</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>455876</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7037566</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>121601938</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79656</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>455844</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7037605</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande rönn (23 cm dbh)  i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>121601573</v>
+      </c>
+      <c r="B31" t="n">
+        <v>74715</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>455805</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7037437</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121598525</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Kläppberget, Kläppberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>455852</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7037584</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På gammal gran och björk</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>August Nordin</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121601754</v>
+      </c>
+      <c r="B33" t="n">
+        <v>74715</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>455761</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7037494</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121598771</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Kläppberget, Kläppberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>455915</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7037655</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På gammal/gamla granar</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, August Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121599091</v>
+      </c>
+      <c r="B35" t="n">
+        <v>74715</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kläppberget, Kläppberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>455970</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7037654</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121601528</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>455821</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7037413</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt på gamla granar</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>121601941</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79650</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>455844</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7037605</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På rönn</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>121598974</v>
+      </c>
+      <c r="B38" t="n">
+        <v>90685</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>455990</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7037625</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På gren på gammal gran</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>121598940</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79079</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1797</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mjölig dropplav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Cliostomum leprosum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>455950</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7037593</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal levande gran (55 cm dbh, ca 150 år gammal</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>121601743</v>
+      </c>
+      <c r="B40" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>455781</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7037490</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>121601169</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79719</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>455919</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7037597</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande rönn 23 cm dbh i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>121601436</v>
+      </c>
+      <c r="B42" t="n">
+        <v>74699</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>455851</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7037441</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På ved på lyra vid basen av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>121598582</v>
+      </c>
+      <c r="B43" t="n">
+        <v>74715</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>455834</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7037660</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>121601695</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79719</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>455760</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7037508</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>121598566</v>
+      </c>
+      <c r="B45" t="n">
+        <v>77546</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>455834</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7037660</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (42 cm dbh, ca 150 år) i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>121601448</v>
+      </c>
+      <c r="B46" t="n">
+        <v>74706</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>492</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Smalskaftslav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Chaenotheca gracilenta</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>455851</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7037441</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På ved på lyra vid basen av glasbjörk</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>121598798</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>455956</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7037592</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På gammal gran i gammal granskog</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>121598839</v>
+      </c>
+      <c r="B48" t="n">
+        <v>74715</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Kläppberget, Kläppberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>455930</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7037619</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>121598649</v>
+      </c>
+      <c r="B49" t="n">
+        <v>74713</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6486</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Skuggnål</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Chaenotheca sphaerocephala</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>455868</v>
+      </c>
+      <c r="R49" t="n">
+        <v>7037664</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På bark i hålighet vid basen av grov gammal gran (50 cm dbh,  ca 150)</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>121598668</v>
+      </c>
+      <c r="B50" t="n">
+        <v>74527</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6428</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Rostfläck</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Arthonia vinosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>455858</v>
+      </c>
+      <c r="R50" t="n">
+        <v>7037672</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal gran</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>121599065</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79041</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>1778</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Fjällig knopplav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Biatora fallax</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Hepp</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>456010</v>
+      </c>
+      <c r="R51" t="n">
+        <v>7037665</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På bark på rotben på gammal gran i brant</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>121598734</v>
+      </c>
+      <c r="B52" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>455911</v>
+      </c>
+      <c r="R52" t="n">
+        <v>7037653</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 28823-2024 artfynd.xlsx
+++ b/artfynd/A 28823-2024 artfynd.xlsx
@@ -3160,7 +3160,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121601584</v>
+        <v>121598771</v>
       </c>
       <c r="B22" t="n">
         <v>78609</v>
@@ -3193,17 +3193,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455813</v>
+        <v>455915</v>
       </c>
       <c r="R22" t="n">
-        <v>7037433</v>
+        <v>7037655</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3235,7 +3244,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3245,12 +3254,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt på glasbjörk i gammal granskog, längsta bål 40 cm</t>
+          <t>På gammal/gamla granar</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3265,22 +3274,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121601174</v>
+        <v>121598649</v>
       </c>
       <c r="B23" t="n">
-        <v>74715</v>
+        <v>74713</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3289,46 +3298,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6440</v>
+        <v>6486</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455933</v>
+        <v>455868</v>
       </c>
       <c r="R23" t="n">
-        <v>7037605</v>
+        <v>7037664</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3357,7 +3361,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3367,12 +3371,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark i hålighet vid basen av grov gammal gran (50 cm dbh,  ca 150)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3387,22 +3391,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121601908</v>
+        <v>121601695</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>79719</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3411,47 +3415,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455848</v>
+        <v>455760</v>
       </c>
       <c r="R24" t="n">
-        <v>7037606</v>
+        <v>7037508</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3483,7 +3478,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3493,12 +3488,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal grov gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3525,10 +3520,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121598835</v>
+        <v>121598839</v>
       </c>
       <c r="B25" t="n">
-        <v>78865</v>
+        <v>74715</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3537,38 +3532,43 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6459</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455963</v>
+        <v>455930</v>
       </c>
       <c r="R25" t="n">
-        <v>7037616</v>
+        <v>7037619</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3610,12 +3610,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På gren på gammal gran</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3630,22 +3625,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121598520</v>
+        <v>121598974</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>90685</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3654,50 +3649,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455831</v>
+        <v>455990</v>
       </c>
       <c r="R26" t="n">
-        <v>7037676</v>
+        <v>7037625</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3726,7 +3712,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3736,12 +3722,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gren på gammal gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3756,22 +3742,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin, August Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121599010</v>
+        <v>121601941</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>79650</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3780,50 +3766,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455998</v>
+        <v>455844</v>
       </c>
       <c r="R27" t="n">
-        <v>7037645</v>
+        <v>7037605</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3852,7 +3829,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3862,12 +3839,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal gran, mer än 200 bålar, granen 55 cm dbh.</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3894,10 +3871,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121598559</v>
+        <v>121601584</v>
       </c>
       <c r="B28" t="n">
-        <v>79079</v>
+        <v>78609</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3910,42 +3887,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1797</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455834</v>
+        <v>455813</v>
       </c>
       <c r="R28" t="n">
-        <v>7037660</v>
+        <v>7037433</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3974,7 +3946,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3984,12 +3956,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
+          <t>Rikligt på glasbjörk i gammal granskog, längsta bål 40 cm</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4016,10 +3988,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121601299</v>
+        <v>121601174</v>
       </c>
       <c r="B29" t="n">
-        <v>90720</v>
+        <v>74715</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4032,34 +4004,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455876</v>
+        <v>455933</v>
       </c>
       <c r="R29" t="n">
-        <v>7037566</v>
+        <v>7037605</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4091,7 +4068,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4101,12 +4078,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4121,12 +4098,12 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -4250,10 +4227,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121601573</v>
+        <v>121598835</v>
       </c>
       <c r="B31" t="n">
-        <v>74715</v>
+        <v>78865</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4262,25 +4239,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6459</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4290,10 +4267,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455805</v>
+        <v>455963</v>
       </c>
       <c r="R31" t="n">
-        <v>7037437</v>
+        <v>7037616</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4325,7 +4302,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4335,12 +4312,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gren på gammal gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4367,7 +4344,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121598525</v>
+        <v>121598798</v>
       </c>
       <c r="B32" t="n">
         <v>78609</v>
@@ -4412,14 +4389,14 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455852</v>
+        <v>455956</v>
       </c>
       <c r="R32" t="n">
-        <v>7037584</v>
+        <v>7037592</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4451,7 +4428,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4461,12 +4438,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal gran och björk</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4481,12 +4458,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4610,10 +4587,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121598771</v>
+        <v>121599091</v>
       </c>
       <c r="B34" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4626,31 +4603,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4659,10 +4632,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455915</v>
+        <v>455970</v>
       </c>
       <c r="R34" t="n">
-        <v>7037655</v>
+        <v>7037654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4694,7 +4667,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4704,12 +4677,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal/gamla granar</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4729,17 +4702,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121599091</v>
+        <v>121599010</v>
       </c>
       <c r="B35" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4752,42 +4725,46 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455970</v>
+        <v>455998</v>
       </c>
       <c r="R35" t="n">
-        <v>7037654</v>
+        <v>7037645</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4816,7 +4793,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4826,12 +4803,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran, mer än 200 bålar, granen 55 cm dbh.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4846,22 +4823,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121601528</v>
+        <v>121601448</v>
       </c>
       <c r="B36" t="n">
-        <v>78609</v>
+        <v>74706</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4870,47 +4847,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455821</v>
+        <v>455851</v>
       </c>
       <c r="R36" t="n">
-        <v>7037413</v>
+        <v>7037441</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4942,7 +4910,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4952,12 +4920,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar</t>
+          <t>På ved på lyra vid basen av glasbjörk</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4984,10 +4952,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121601941</v>
+        <v>121599065</v>
       </c>
       <c r="B37" t="n">
-        <v>79650</v>
+        <v>79041</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4996,25 +4964,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>229497</v>
+        <v>1778</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5024,10 +4992,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455844</v>
+        <v>456010</v>
       </c>
       <c r="R37" t="n">
-        <v>7037605</v>
+        <v>7037665</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5059,7 +5027,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5069,12 +5037,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>På bark på rotben på gammal gran i brant</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5101,10 +5069,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121598974</v>
+        <v>121601169</v>
       </c>
       <c r="B38" t="n">
-        <v>90685</v>
+        <v>79719</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5117,21 +5085,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5141,13 +5109,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455990</v>
+        <v>455919</v>
       </c>
       <c r="R38" t="n">
-        <v>7037625</v>
+        <v>7037597</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5176,7 +5144,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5186,12 +5154,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gren på gammal gran</t>
+          <t>På bark på stam av levande rönn 23 cm dbh i gammal granskog</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5218,10 +5186,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121598940</v>
+        <v>121601573</v>
       </c>
       <c r="B39" t="n">
-        <v>79079</v>
+        <v>74715</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5234,21 +5202,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1797</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5258,10 +5226,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455950</v>
+        <v>455805</v>
       </c>
       <c r="R39" t="n">
-        <v>7037593</v>
+        <v>7037437</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5293,7 +5261,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5303,12 +5271,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran (55 cm dbh, ca 150 år gammal</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5335,10 +5303,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121601743</v>
+        <v>121598668</v>
       </c>
       <c r="B40" t="n">
-        <v>78609</v>
+        <v>74527</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5347,47 +5315,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455781</v>
+        <v>455858</v>
       </c>
       <c r="R40" t="n">
-        <v>7037490</v>
+        <v>7037672</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5419,7 +5378,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5429,12 +5388,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark vid basen av gammal gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5461,10 +5420,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121601169</v>
+        <v>121598520</v>
       </c>
       <c r="B41" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5473,41 +5432,50 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455919</v>
+        <v>455831</v>
       </c>
       <c r="R41" t="n">
-        <v>7037597</v>
+        <v>7037676</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5536,7 +5504,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5546,12 +5514,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På bark på stam av levande rönn 23 cm dbh i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5566,22 +5534,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121601436</v>
+        <v>121601743</v>
       </c>
       <c r="B42" t="n">
-        <v>74699</v>
+        <v>78609</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5590,38 +5558,47 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455851</v>
+        <v>455781</v>
       </c>
       <c r="R42" t="n">
-        <v>7037441</v>
+        <v>7037490</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5653,7 +5630,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5663,12 +5640,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av glasbjörk</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5695,10 +5672,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121598582</v>
+        <v>121598525</v>
       </c>
       <c r="B43" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5711,34 +5688,43 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455834</v>
+        <v>455852</v>
       </c>
       <c r="R43" t="n">
-        <v>7037660</v>
+        <v>7037584</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5770,7 +5756,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5780,12 +5766,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gammal gran och björk</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5800,22 +5786,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121601695</v>
+        <v>121598734</v>
       </c>
       <c r="B44" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5824,38 +5810,47 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455760</v>
+        <v>455911</v>
       </c>
       <c r="R44" t="n">
-        <v>7037508</v>
+        <v>7037653</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5887,7 +5882,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5897,12 +5892,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5929,10 +5924,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121598566</v>
+        <v>121598559</v>
       </c>
       <c r="B45" t="n">
-        <v>77546</v>
+        <v>79079</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5945,24 +5940,29 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228579</v>
+        <v>1797</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
@@ -5975,7 +5975,7 @@
         <v>7037660</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (42 cm dbh, ca 150 år) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6046,10 +6046,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121601448</v>
+        <v>121598940</v>
       </c>
       <c r="B46" t="n">
-        <v>74706</v>
+        <v>79079</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6058,25 +6058,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>492</v>
+        <v>1797</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6086,10 +6086,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455851</v>
+        <v>455950</v>
       </c>
       <c r="R46" t="n">
-        <v>7037441</v>
+        <v>7037593</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av glasbjörk</t>
+          <t>På bark vid basen av gammal levande gran (55 cm dbh, ca 150 år gammal</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6163,7 +6163,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121598798</v>
+        <v>121601908</v>
       </c>
       <c r="B47" t="n">
         <v>78609</v>
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455956</v>
+        <v>455848</v>
       </c>
       <c r="R47" t="n">
-        <v>7037592</v>
+        <v>7037606</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal grov gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6289,7 +6289,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121598839</v>
+        <v>121598582</v>
       </c>
       <c r="B48" t="n">
         <v>74715</v>
@@ -6323,21 +6323,16 @@
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455930</v>
+        <v>455834</v>
       </c>
       <c r="R48" t="n">
-        <v>7037619</v>
+        <v>7037660</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6369,7 +6364,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6379,7 +6374,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6394,22 +6394,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121598649</v>
+        <v>121601299</v>
       </c>
       <c r="B49" t="n">
-        <v>74713</v>
+        <v>90720</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6418,25 +6418,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6486</v>
+        <v>1202</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6446,13 +6446,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455868</v>
+        <v>455876</v>
       </c>
       <c r="R49" t="n">
-        <v>7037664</v>
+        <v>7037566</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av grov gammal gran (50 cm dbh,  ca 150)</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6523,10 +6523,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121598668</v>
+        <v>121601528</v>
       </c>
       <c r="B50" t="n">
-        <v>74527</v>
+        <v>78609</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6535,38 +6535,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455858</v>
+        <v>455821</v>
       </c>
       <c r="R50" t="n">
-        <v>7037672</v>
+        <v>7037413</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6598,7 +6607,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6608,12 +6617,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal gran</t>
+          <t>Rikligt på gamla granar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6640,10 +6649,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121599065</v>
+        <v>121598566</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>77546</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6652,25 +6661,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1778</v>
+        <v>228579</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6680,10 +6689,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456010</v>
+        <v>455834</v>
       </c>
       <c r="R51" t="n">
-        <v>7037665</v>
+        <v>7037660</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6715,7 +6724,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6725,12 +6734,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På bark på rotben på gammal gran i brant</t>
+          <t>På bark på stam av levande gammal gran (42 cm dbh, ca 150 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6757,10 +6766,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121598734</v>
+        <v>121601436</v>
       </c>
       <c r="B52" t="n">
-        <v>78609</v>
+        <v>74699</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6769,47 +6778,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455911</v>
+        <v>455851</v>
       </c>
       <c r="R52" t="n">
-        <v>7037653</v>
+        <v>7037441</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På ved på lyra vid basen av glasbjörk</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 28823-2024 artfynd.xlsx
+++ b/artfynd/A 28823-2024 artfynd.xlsx
@@ -3160,10 +3160,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121598771</v>
+        <v>121598559</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>79079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3176,46 +3176,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1797</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455915</v>
+        <v>455834</v>
       </c>
       <c r="R22" t="n">
-        <v>7037655</v>
+        <v>7037660</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3244,7 +3240,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3254,12 +3250,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal/gamla granar</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3274,22 +3270,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121598649</v>
+        <v>121598734</v>
       </c>
       <c r="B23" t="n">
-        <v>74713</v>
+        <v>78609</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3298,41 +3294,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455868</v>
+        <v>455911</v>
       </c>
       <c r="R23" t="n">
-        <v>7037664</v>
+        <v>7037653</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3361,7 +3366,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3371,12 +3376,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av grov gammal gran (50 cm dbh,  ca 150)</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3403,10 +3408,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121601695</v>
+        <v>121598668</v>
       </c>
       <c r="B24" t="n">
-        <v>79719</v>
+        <v>74527</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3419,21 +3424,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6462</v>
+        <v>6428</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3443,10 +3448,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455760</v>
+        <v>455858</v>
       </c>
       <c r="R24" t="n">
-        <v>7037508</v>
+        <v>7037672</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3478,7 +3483,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3488,12 +3493,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På bark vid basen av gammal gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3520,10 +3525,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121598839</v>
+        <v>121598566</v>
       </c>
       <c r="B25" t="n">
-        <v>74715</v>
+        <v>77546</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3536,39 +3541,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455930</v>
+        <v>455834</v>
       </c>
       <c r="R25" t="n">
-        <v>7037619</v>
+        <v>7037660</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3610,7 +3610,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran (42 cm dbh, ca 150 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3625,22 +3630,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121598974</v>
+        <v>121601584</v>
       </c>
       <c r="B26" t="n">
-        <v>90685</v>
+        <v>78609</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3649,25 +3654,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3677,10 +3682,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455990</v>
+        <v>455813</v>
       </c>
       <c r="R26" t="n">
-        <v>7037625</v>
+        <v>7037433</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3712,7 +3717,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3722,12 +3727,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gren på gammal gran</t>
+          <t>Rikligt på glasbjörk i gammal granskog, längsta bål 40 cm</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3754,10 +3759,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121601941</v>
+        <v>121598649</v>
       </c>
       <c r="B27" t="n">
-        <v>79650</v>
+        <v>74713</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3766,25 +3771,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229497</v>
+        <v>6486</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3794,13 +3799,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455844</v>
+        <v>455868</v>
       </c>
       <c r="R27" t="n">
-        <v>7037605</v>
+        <v>7037664</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3829,7 +3834,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3839,12 +3844,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>På bark i hålighet vid basen av grov gammal gran (50 cm dbh,  ca 150)</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3871,10 +3876,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121601584</v>
+        <v>121598582</v>
       </c>
       <c r="B28" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3887,21 +3892,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3911,10 +3916,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455813</v>
+        <v>455834</v>
       </c>
       <c r="R28" t="n">
-        <v>7037433</v>
+        <v>7037660</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3946,7 +3951,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3956,12 +3961,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt på glasbjörk i gammal granskog, längsta bål 40 cm</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3988,10 +3993,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121601174</v>
+        <v>121601908</v>
       </c>
       <c r="B29" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4004,39 +4009,43 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455933</v>
+        <v>455848</v>
       </c>
       <c r="R29" t="n">
-        <v>7037605</v>
+        <v>7037606</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4068,7 +4077,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4078,12 +4087,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal grov gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4098,22 +4107,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121601938</v>
+        <v>121601743</v>
       </c>
       <c r="B30" t="n">
-        <v>79656</v>
+        <v>78609</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4122,38 +4131,47 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455844</v>
+        <v>455781</v>
       </c>
       <c r="R30" t="n">
-        <v>7037605</v>
+        <v>7037490</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4185,7 +4203,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4195,12 +4213,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På bark på stam av levande rönn (23 cm dbh)  i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4227,10 +4245,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121598835</v>
+        <v>121601573</v>
       </c>
       <c r="B31" t="n">
-        <v>78865</v>
+        <v>74715</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4239,25 +4257,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6459</v>
+        <v>6440</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4267,10 +4285,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455963</v>
+        <v>455805</v>
       </c>
       <c r="R31" t="n">
-        <v>7037616</v>
+        <v>7037437</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4302,7 +4320,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4312,12 +4330,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gren på gammal gran</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4344,10 +4362,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121598798</v>
+        <v>121601174</v>
       </c>
       <c r="B32" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4360,43 +4378,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455956</v>
+        <v>455933</v>
       </c>
       <c r="R32" t="n">
-        <v>7037592</v>
+        <v>7037605</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4428,7 +4442,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4438,12 +4452,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4458,22 +4472,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121601754</v>
+        <v>121601695</v>
       </c>
       <c r="B33" t="n">
-        <v>74715</v>
+        <v>79719</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4482,25 +4496,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4510,10 +4524,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455761</v>
+        <v>455760</v>
       </c>
       <c r="R33" t="n">
-        <v>7037494</v>
+        <v>7037508</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4545,7 +4559,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4555,12 +4569,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4587,10 +4601,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121599091</v>
+        <v>121601941</v>
       </c>
       <c r="B34" t="n">
-        <v>74715</v>
+        <v>79650</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4599,43 +4613,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6440</v>
+        <v>229497</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455970</v>
+        <v>455844</v>
       </c>
       <c r="R34" t="n">
-        <v>7037654</v>
+        <v>7037605</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4667,7 +4676,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4677,12 +4686,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4697,22 +4706,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121599010</v>
+        <v>121598835</v>
       </c>
       <c r="B35" t="n">
-        <v>78609</v>
+        <v>78865</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4721,50 +4730,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6459</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Flot.) Kullh.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455998</v>
+        <v>455963</v>
       </c>
       <c r="R35" t="n">
-        <v>7037645</v>
+        <v>7037616</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal gran, mer än 200 bålar, granen 55 cm dbh.</t>
+          <t>På gren på gammal gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4835,10 +4835,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121601448</v>
+        <v>121599010</v>
       </c>
       <c r="B36" t="n">
-        <v>74706</v>
+        <v>78609</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4847,41 +4847,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>492</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455851</v>
+        <v>455998</v>
       </c>
       <c r="R36" t="n">
-        <v>7037441</v>
+        <v>7037645</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4910,7 +4919,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4920,12 +4929,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av glasbjörk</t>
+          <t>På gammal gran, mer än 200 bålar, granen 55 cm dbh.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4952,10 +4961,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121599065</v>
+        <v>121601436</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>74699</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4964,25 +4973,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1778</v>
+        <v>6439</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4992,10 +5001,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>456010</v>
+        <v>455851</v>
       </c>
       <c r="R37" t="n">
-        <v>7037665</v>
+        <v>7037441</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5027,7 +5036,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5037,12 +5046,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark på rotben på gammal gran i brant</t>
+          <t>På ved på lyra vid basen av glasbjörk</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5069,10 +5078,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121601169</v>
+        <v>121598940</v>
       </c>
       <c r="B38" t="n">
-        <v>79719</v>
+        <v>79079</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5081,25 +5090,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6462</v>
+        <v>1797</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5109,13 +5118,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455919</v>
+        <v>455950</v>
       </c>
       <c r="R38" t="n">
-        <v>7037597</v>
+        <v>7037593</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5144,7 +5153,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5154,12 +5163,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På bark på stam av levande rönn 23 cm dbh i gammal granskog</t>
+          <t>På bark vid basen av gammal levande gran (55 cm dbh, ca 150 år gammal</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5186,10 +5195,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121601573</v>
+        <v>121601528</v>
       </c>
       <c r="B39" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5202,34 +5211,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455805</v>
+        <v>455821</v>
       </c>
       <c r="R39" t="n">
-        <v>7037437</v>
+        <v>7037413</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5261,7 +5279,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5271,12 +5289,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>Rikligt på gamla granar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5303,10 +5321,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121598668</v>
+        <v>121599091</v>
       </c>
       <c r="B40" t="n">
-        <v>74527</v>
+        <v>74715</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5315,38 +5333,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6428</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455858</v>
+        <v>455970</v>
       </c>
       <c r="R40" t="n">
-        <v>7037672</v>
+        <v>7037654</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5378,7 +5401,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5388,12 +5411,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5408,19 +5431,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121598520</v>
+        <v>121598771</v>
       </c>
       <c r="B41" t="n">
         <v>78609</v>
@@ -5455,7 +5478,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5469,13 +5492,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455831</v>
+        <v>455915</v>
       </c>
       <c r="R41" t="n">
-        <v>7037676</v>
+        <v>7037655</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5504,7 +5527,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5514,12 +5537,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal/gamla granar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5539,14 +5562,14 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin, August Nordin</t>
+          <t>Ludvig Nordin, August Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121601743</v>
+        <v>121598798</v>
       </c>
       <c r="B42" t="n">
         <v>78609</v>
@@ -5595,10 +5618,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455781</v>
+        <v>455956</v>
       </c>
       <c r="R42" t="n">
-        <v>7037490</v>
+        <v>7037592</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5630,7 +5653,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5640,12 +5663,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5672,10 +5695,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121598525</v>
+        <v>121601448</v>
       </c>
       <c r="B43" t="n">
-        <v>78609</v>
+        <v>74706</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5684,47 +5707,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455852</v>
+        <v>455851</v>
       </c>
       <c r="R43" t="n">
-        <v>7037584</v>
+        <v>7037441</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5756,7 +5770,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5766,12 +5780,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal gran och björk</t>
+          <t>På ved på lyra vid basen av glasbjörk</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5786,19 +5800,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121598734</v>
+        <v>121598525</v>
       </c>
       <c r="B44" t="n">
         <v>78609</v>
@@ -5843,14 +5857,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455911</v>
+        <v>455852</v>
       </c>
       <c r="R44" t="n">
-        <v>7037653</v>
+        <v>7037584</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5882,7 +5896,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5892,12 +5906,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran och björk</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5912,22 +5926,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121598559</v>
+        <v>121601299</v>
       </c>
       <c r="B45" t="n">
-        <v>79079</v>
+        <v>90720</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5940,42 +5954,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1797</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455834</v>
+        <v>455876</v>
       </c>
       <c r="R45" t="n">
-        <v>7037660</v>
+        <v>7037566</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6004,7 +6013,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6014,12 +6023,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6039,17 +6048,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121598940</v>
+        <v>121598520</v>
       </c>
       <c r="B46" t="n">
-        <v>79079</v>
+        <v>78609</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6062,37 +6071,46 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1797</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455950</v>
+        <v>455831</v>
       </c>
       <c r="R46" t="n">
-        <v>7037593</v>
+        <v>7037676</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6121,7 +6139,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6131,12 +6149,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran (55 cm dbh, ca 150 år gammal</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6151,22 +6169,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121601908</v>
+        <v>121598839</v>
       </c>
       <c r="B47" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6179,43 +6197,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455848</v>
+        <v>455930</v>
       </c>
       <c r="R47" t="n">
-        <v>7037606</v>
+        <v>7037619</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6247,7 +6261,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6257,12 +6271,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På gammal grov gran</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6277,22 +6286,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121598582</v>
+        <v>121598974</v>
       </c>
       <c r="B48" t="n">
-        <v>74715</v>
+        <v>90685</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6301,25 +6310,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6440</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6329,10 +6338,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455834</v>
+        <v>455990</v>
       </c>
       <c r="R48" t="n">
-        <v>7037660</v>
+        <v>7037625</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6364,7 +6373,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6374,12 +6383,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gren på gammal gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6406,10 +6415,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121601299</v>
+        <v>121601169</v>
       </c>
       <c r="B49" t="n">
-        <v>90720</v>
+        <v>79719</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6418,25 +6427,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6446,13 +6455,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455876</v>
+        <v>455919</v>
       </c>
       <c r="R49" t="n">
-        <v>7037566</v>
+        <v>7037597</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6481,7 +6490,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6491,12 +6500,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På bark på stam av levande rönn 23 cm dbh i gammal granskog</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6523,10 +6532,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121601528</v>
+        <v>121601754</v>
       </c>
       <c r="B50" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6539,43 +6548,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455821</v>
+        <v>455761</v>
       </c>
       <c r="R50" t="n">
-        <v>7037413</v>
+        <v>7037494</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6649,10 +6649,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121598566</v>
+        <v>121601938</v>
       </c>
       <c r="B51" t="n">
-        <v>77546</v>
+        <v>79656</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6661,25 +6661,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228579</v>
+        <v>229748</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455834</v>
+        <v>455844</v>
       </c>
       <c r="R51" t="n">
-        <v>7037660</v>
+        <v>7037605</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (42 cm dbh, ca 150 år) i gammal granskog</t>
+          <t>På bark på stam av levande rönn (23 cm dbh)  i gammal granskog</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6759,17 +6759,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121601436</v>
+        <v>121599065</v>
       </c>
       <c r="B52" t="n">
-        <v>74699</v>
+        <v>79041</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6778,25 +6778,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6439</v>
+        <v>1778</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455851</v>
+        <v>456010</v>
       </c>
       <c r="R52" t="n">
-        <v>7037441</v>
+        <v>7037665</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av glasbjörk</t>
+          <t>På bark på rotben på gammal gran i brant</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 28823-2024 artfynd.xlsx
+++ b/artfynd/A 28823-2024 artfynd.xlsx
@@ -3160,10 +3160,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121598559</v>
+        <v>121598798</v>
       </c>
       <c r="B22" t="n">
-        <v>79079</v>
+        <v>78609</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3176,27 +3176,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1797</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3205,13 +3209,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455834</v>
+        <v>455956</v>
       </c>
       <c r="R22" t="n">
-        <v>7037660</v>
+        <v>7037592</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3240,7 +3244,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3250,12 +3254,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3282,10 +3286,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121598734</v>
+        <v>121598649</v>
       </c>
       <c r="B23" t="n">
-        <v>78609</v>
+        <v>74713</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3294,50 +3298,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455911</v>
+        <v>455868</v>
       </c>
       <c r="R23" t="n">
-        <v>7037653</v>
+        <v>7037664</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3366,7 +3361,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3376,12 +3371,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark i hålighet vid basen av grov gammal gran (50 cm dbh,  ca 150)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3408,10 +3403,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121598668</v>
+        <v>121601528</v>
       </c>
       <c r="B24" t="n">
-        <v>74527</v>
+        <v>78609</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3420,38 +3415,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455858</v>
+        <v>455821</v>
       </c>
       <c r="R24" t="n">
-        <v>7037672</v>
+        <v>7037413</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3483,7 +3487,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3493,12 +3497,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal gran</t>
+          <t>Rikligt på gamla granar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3525,10 +3529,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121598566</v>
+        <v>121598582</v>
       </c>
       <c r="B25" t="n">
-        <v>77546</v>
+        <v>74715</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3541,21 +3545,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3615,7 +3619,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (42 cm dbh, ca 150 år) i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3642,10 +3646,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121601584</v>
+        <v>121598566</v>
       </c>
       <c r="B26" t="n">
-        <v>78609</v>
+        <v>77546</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3658,21 +3662,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3682,10 +3686,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455813</v>
+        <v>455834</v>
       </c>
       <c r="R26" t="n">
-        <v>7037433</v>
+        <v>7037660</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3717,7 +3721,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3727,12 +3731,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt på glasbjörk i gammal granskog, längsta bål 40 cm</t>
+          <t>På bark på stam av levande gammal gran (42 cm dbh, ca 150 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3759,10 +3763,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121598649</v>
+        <v>121598525</v>
       </c>
       <c r="B27" t="n">
-        <v>74713</v>
+        <v>78609</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3771,41 +3775,50 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455868</v>
+        <v>455852</v>
       </c>
       <c r="R27" t="n">
-        <v>7037664</v>
+        <v>7037584</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3834,7 +3847,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3844,12 +3857,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av grov gammal gran (50 cm dbh,  ca 150)</t>
+          <t>På gammal gran och björk</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3864,22 +3877,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121598582</v>
+        <v>121598835</v>
       </c>
       <c r="B28" t="n">
-        <v>74715</v>
+        <v>78865</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3888,25 +3901,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>6459</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3916,10 +3929,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455834</v>
+        <v>455963</v>
       </c>
       <c r="R28" t="n">
-        <v>7037660</v>
+        <v>7037616</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3951,7 +3964,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3961,12 +3974,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gren på gammal gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3993,10 +4006,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121601908</v>
+        <v>121601169</v>
       </c>
       <c r="B29" t="n">
-        <v>78609</v>
+        <v>79719</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4005,50 +4018,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455848</v>
+        <v>455919</v>
       </c>
       <c r="R29" t="n">
-        <v>7037606</v>
+        <v>7037597</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4077,7 +4081,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4087,12 +4091,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På gammal grov gran</t>
+          <t>På bark på stam av levande rönn 23 cm dbh i gammal granskog</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4112,17 +4116,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121601743</v>
+        <v>121601174</v>
       </c>
       <c r="B30" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4135,43 +4139,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455781</v>
+        <v>455933</v>
       </c>
       <c r="R30" t="n">
-        <v>7037490</v>
+        <v>7037605</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4203,7 +4203,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4233,22 +4233,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121601573</v>
+        <v>121601743</v>
       </c>
       <c r="B31" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4261,34 +4261,43 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455805</v>
+        <v>455781</v>
       </c>
       <c r="R31" t="n">
-        <v>7037437</v>
+        <v>7037490</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4320,7 +4329,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4330,12 +4339,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4362,10 +4371,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121601174</v>
+        <v>121601436</v>
       </c>
       <c r="B32" t="n">
-        <v>74715</v>
+        <v>74699</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4374,43 +4383,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455933</v>
+        <v>455851</v>
       </c>
       <c r="R32" t="n">
-        <v>7037605</v>
+        <v>7037441</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4442,7 +4446,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4452,12 +4456,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På ved på lyra vid basen av glasbjörk</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4472,22 +4476,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121601695</v>
+        <v>121598668</v>
       </c>
       <c r="B33" t="n">
-        <v>79719</v>
+        <v>74527</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4500,21 +4504,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6462</v>
+        <v>6428</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4524,10 +4528,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455760</v>
+        <v>455858</v>
       </c>
       <c r="R33" t="n">
-        <v>7037508</v>
+        <v>7037672</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4559,7 +4563,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4569,12 +4573,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På bark vid basen av gammal gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4601,10 +4605,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121601941</v>
+        <v>121601754</v>
       </c>
       <c r="B34" t="n">
-        <v>79650</v>
+        <v>74715</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4613,25 +4617,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229497</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4641,10 +4645,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455844</v>
+        <v>455761</v>
       </c>
       <c r="R34" t="n">
-        <v>7037605</v>
+        <v>7037494</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4676,7 +4680,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4686,12 +4690,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4718,10 +4722,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121598835</v>
+        <v>121598734</v>
       </c>
       <c r="B35" t="n">
-        <v>78865</v>
+        <v>78609</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4730,38 +4734,47 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6459</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455963</v>
+        <v>455911</v>
       </c>
       <c r="R35" t="n">
-        <v>7037616</v>
+        <v>7037653</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4793,7 +4806,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4803,12 +4816,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gren på gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4828,17 +4841,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121599010</v>
+        <v>121601941</v>
       </c>
       <c r="B36" t="n">
-        <v>78609</v>
+        <v>79650</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4847,50 +4860,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455998</v>
+        <v>455844</v>
       </c>
       <c r="R36" t="n">
-        <v>7037645</v>
+        <v>7037605</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4919,7 +4923,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4929,12 +4933,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gammal gran, mer än 200 bålar, granen 55 cm dbh.</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4961,10 +4965,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121601436</v>
+        <v>121598940</v>
       </c>
       <c r="B37" t="n">
-        <v>74699</v>
+        <v>79079</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4973,25 +4977,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6439</v>
+        <v>1797</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5001,10 +5005,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455851</v>
+        <v>455950</v>
       </c>
       <c r="R37" t="n">
-        <v>7037441</v>
+        <v>7037593</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5036,7 +5040,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5046,12 +5050,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av glasbjörk</t>
+          <t>På bark vid basen av gammal levande gran (55 cm dbh, ca 150 år gammal</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5078,10 +5082,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121598940</v>
+        <v>121599091</v>
       </c>
       <c r="B38" t="n">
-        <v>79079</v>
+        <v>74715</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5094,34 +5098,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1797</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455950</v>
+        <v>455970</v>
       </c>
       <c r="R38" t="n">
-        <v>7037593</v>
+        <v>7037654</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5153,7 +5162,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5163,12 +5172,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran (55 cm dbh, ca 150 år gammal</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5183,22 +5192,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121601528</v>
+        <v>121598839</v>
       </c>
       <c r="B39" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5211,43 +5220,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455821</v>
+        <v>455930</v>
       </c>
       <c r="R39" t="n">
-        <v>7037413</v>
+        <v>7037619</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5279,7 +5284,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5289,12 +5294,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt på gamla granar</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5309,22 +5309,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121599091</v>
+        <v>121599010</v>
       </c>
       <c r="B40" t="n">
-        <v>74715</v>
+        <v>78609</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5337,42 +5337,46 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455970</v>
+        <v>455998</v>
       </c>
       <c r="R40" t="n">
-        <v>7037654</v>
+        <v>7037645</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5401,7 +5405,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5411,12 +5415,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran, mer än 200 bålar, granen 55 cm dbh.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5431,19 +5435,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121598771</v>
+        <v>121598520</v>
       </c>
       <c r="B41" t="n">
         <v>78609</v>
@@ -5478,7 +5482,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -5492,13 +5496,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455915</v>
+        <v>455831</v>
       </c>
       <c r="R41" t="n">
-        <v>7037655</v>
+        <v>7037676</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5527,7 +5531,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5537,12 +5541,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal/gamla granar</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5562,14 +5566,14 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121598798</v>
+        <v>121598771</v>
       </c>
       <c r="B42" t="n">
         <v>78609</v>
@@ -5614,14 +5618,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455956</v>
+        <v>455915</v>
       </c>
       <c r="R42" t="n">
-        <v>7037592</v>
+        <v>7037655</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5653,7 +5657,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5663,12 +5667,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal/gamla granar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5683,22 +5687,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121601448</v>
+        <v>121598974</v>
       </c>
       <c r="B43" t="n">
-        <v>74706</v>
+        <v>90685</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5707,25 +5711,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>492</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5735,10 +5739,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455851</v>
+        <v>455990</v>
       </c>
       <c r="R43" t="n">
-        <v>7037441</v>
+        <v>7037625</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5770,7 +5774,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5780,12 +5784,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av glasbjörk</t>
+          <t>På gren på gammal gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5812,10 +5816,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121598525</v>
+        <v>121599065</v>
       </c>
       <c r="B44" t="n">
-        <v>78609</v>
+        <v>79041</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5824,47 +5828,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1778</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Hepp</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455852</v>
+        <v>456010</v>
       </c>
       <c r="R44" t="n">
-        <v>7037584</v>
+        <v>7037665</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5896,7 +5891,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5906,12 +5901,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gammal gran och björk</t>
+          <t>På bark på rotben på gammal gran i brant</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5926,22 +5921,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121601299</v>
+        <v>121601695</v>
       </c>
       <c r="B45" t="n">
-        <v>90720</v>
+        <v>79719</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5950,25 +5945,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5978,10 +5973,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455876</v>
+        <v>455760</v>
       </c>
       <c r="R45" t="n">
-        <v>7037566</v>
+        <v>7037508</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6013,7 +6008,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6023,12 +6018,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6048,17 +6043,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121598520</v>
+        <v>121601938</v>
       </c>
       <c r="B46" t="n">
-        <v>78609</v>
+        <v>79656</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6067,50 +6062,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455831</v>
+        <v>455844</v>
       </c>
       <c r="R46" t="n">
-        <v>7037676</v>
+        <v>7037605</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6139,7 +6125,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6149,12 +6135,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande rönn (23 cm dbh)  i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6169,19 +6155,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin, August Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121598839</v>
+        <v>121601573</v>
       </c>
       <c r="B47" t="n">
         <v>74715</v>
@@ -6215,21 +6201,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455930</v>
+        <v>455805</v>
       </c>
       <c r="R47" t="n">
-        <v>7037619</v>
+        <v>7037437</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6261,7 +6242,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6271,7 +6252,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6286,22 +6272,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121598974</v>
+        <v>121601908</v>
       </c>
       <c r="B48" t="n">
-        <v>90685</v>
+        <v>78609</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6310,38 +6296,47 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455990</v>
+        <v>455848</v>
       </c>
       <c r="R48" t="n">
-        <v>7037625</v>
+        <v>7037606</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6373,7 +6368,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6383,12 +6378,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gren på gammal gran</t>
+          <t>På gammal grov gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6415,10 +6410,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121601169</v>
+        <v>121601584</v>
       </c>
       <c r="B49" t="n">
-        <v>79719</v>
+        <v>78609</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6427,25 +6422,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6455,13 +6450,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455919</v>
+        <v>455813</v>
       </c>
       <c r="R49" t="n">
-        <v>7037597</v>
+        <v>7037433</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6490,7 +6485,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6500,12 +6495,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På bark på stam av levande rönn 23 cm dbh i gammal granskog</t>
+          <t>Rikligt på glasbjörk i gammal granskog, längsta bål 40 cm</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6532,10 +6527,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121601754</v>
+        <v>121598559</v>
       </c>
       <c r="B50" t="n">
-        <v>74715</v>
+        <v>79079</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6548,37 +6543,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>1797</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455761</v>
+        <v>455834</v>
       </c>
       <c r="R50" t="n">
-        <v>7037494</v>
+        <v>7037660</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6649,10 +6649,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121601938</v>
+        <v>121601299</v>
       </c>
       <c r="B51" t="n">
-        <v>79656</v>
+        <v>90720</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6661,25 +6661,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229748</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455844</v>
+        <v>455876</v>
       </c>
       <c r="R51" t="n">
-        <v>7037605</v>
+        <v>7037566</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På bark på stam av levande rönn (23 cm dbh)  i gammal granskog</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6759,17 +6759,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121599065</v>
+        <v>121601448</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>74706</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6782,21 +6782,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1778</v>
+        <v>492</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6806,10 +6806,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>456010</v>
+        <v>455851</v>
       </c>
       <c r="R52" t="n">
-        <v>7037665</v>
+        <v>7037441</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På bark på rotben på gammal gran i brant</t>
+          <t>På ved på lyra vid basen av glasbjörk</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 28823-2024 artfynd.xlsx
+++ b/artfynd/A 28823-2024 artfynd.xlsx
@@ -5573,10 +5573,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121598771</v>
+        <v>121599065</v>
       </c>
       <c r="B42" t="n">
-        <v>78609</v>
+        <v>79041</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5585,47 +5585,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>1778</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Hepp</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455915</v>
+        <v>456010</v>
       </c>
       <c r="R42" t="n">
-        <v>7037655</v>
+        <v>7037665</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5657,7 +5648,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5667,12 +5658,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal/gamla granar</t>
+          <t>På bark på rotben på gammal gran i brant</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5687,22 +5678,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121598974</v>
+        <v>121598771</v>
       </c>
       <c r="B43" t="n">
-        <v>90685</v>
+        <v>78609</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5711,38 +5702,47 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455990</v>
+        <v>455915</v>
       </c>
       <c r="R43" t="n">
-        <v>7037625</v>
+        <v>7037655</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gren på gammal gran</t>
+          <t>På gammal/gamla granar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5804,22 +5804,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121599065</v>
+        <v>121598974</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>90685</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5828,25 +5828,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1778</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5856,10 +5856,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>456010</v>
+        <v>455990</v>
       </c>
       <c r="R44" t="n">
-        <v>7037665</v>
+        <v>7037625</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På bark på rotben på gammal gran i brant</t>
+          <t>På gren på gammal gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6527,10 +6527,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121598559</v>
+        <v>121601299</v>
       </c>
       <c r="B50" t="n">
-        <v>79079</v>
+        <v>90720</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6543,42 +6543,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1797</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455834</v>
+        <v>455876</v>
       </c>
       <c r="R50" t="n">
-        <v>7037660</v>
+        <v>7037566</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6607,7 +6602,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6617,12 +6612,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6649,10 +6644,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121601299</v>
+        <v>121601448</v>
       </c>
       <c r="B51" t="n">
-        <v>90720</v>
+        <v>74706</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6661,25 +6656,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>492</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6689,10 +6684,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455876</v>
+        <v>455851</v>
       </c>
       <c r="R51" t="n">
-        <v>7037566</v>
+        <v>7037441</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6724,7 +6719,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6734,12 +6729,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På ved på lyra vid basen av glasbjörk</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6766,10 +6761,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121601448</v>
+        <v>121598559</v>
       </c>
       <c r="B52" t="n">
-        <v>74706</v>
+        <v>79079</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6778,41 +6773,46 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>492</v>
+        <v>1797</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455851</v>
+        <v>455834</v>
       </c>
       <c r="R52" t="n">
-        <v>7037441</v>
+        <v>7037660</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av glasbjörk</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 28823-2024 artfynd.xlsx
+++ b/artfynd/A 28823-2024 artfynd.xlsx
@@ -6527,10 +6527,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121601299</v>
+        <v>121598559</v>
       </c>
       <c r="B50" t="n">
-        <v>90720</v>
+        <v>79079</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6543,37 +6543,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>1797</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455876</v>
+        <v>455834</v>
       </c>
       <c r="R50" t="n">
-        <v>7037566</v>
+        <v>7037660</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6602,7 +6607,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6612,12 +6617,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6644,10 +6649,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121601448</v>
+        <v>121601299</v>
       </c>
       <c r="B51" t="n">
-        <v>74706</v>
+        <v>90720</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6656,25 +6661,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>492</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6684,10 +6689,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455851</v>
+        <v>455876</v>
       </c>
       <c r="R51" t="n">
-        <v>7037441</v>
+        <v>7037566</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6719,7 +6724,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6729,12 +6734,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av glasbjörk</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6761,10 +6766,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121598559</v>
+        <v>121601448</v>
       </c>
       <c r="B52" t="n">
-        <v>79079</v>
+        <v>74706</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6773,46 +6778,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1797</v>
+        <v>492</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455834</v>
+        <v>455851</v>
       </c>
       <c r="R52" t="n">
-        <v>7037660</v>
+        <v>7037441</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
+          <t>På ved på lyra vid basen av glasbjörk</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 28823-2024 artfynd.xlsx
+++ b/artfynd/A 28823-2024 artfynd.xlsx
@@ -3160,10 +3160,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121598798</v>
+        <v>121601908</v>
       </c>
       <c r="B22" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3209,10 +3209,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455956</v>
+        <v>455848</v>
       </c>
       <c r="R22" t="n">
-        <v>7037592</v>
+        <v>7037606</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3254,12 +3254,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal grov gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3286,10 +3286,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121598649</v>
+        <v>121601528</v>
       </c>
       <c r="B23" t="n">
-        <v>74713</v>
+        <v>78616</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3298,41 +3298,50 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455868</v>
+        <v>455821</v>
       </c>
       <c r="R23" t="n">
-        <v>7037664</v>
+        <v>7037413</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3361,7 +3370,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3371,12 +3380,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av grov gammal gran (50 cm dbh,  ca 150)</t>
+          <t>Rikligt på gamla granar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3403,10 +3412,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121601528</v>
+        <v>121601941</v>
       </c>
       <c r="B24" t="n">
-        <v>78609</v>
+        <v>79657</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3415,47 +3424,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455821</v>
+        <v>455844</v>
       </c>
       <c r="R24" t="n">
-        <v>7037413</v>
+        <v>7037605</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3497,12 +3497,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3529,10 +3529,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121598582</v>
+        <v>121598798</v>
       </c>
       <c r="B25" t="n">
-        <v>74715</v>
+        <v>78616</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3545,34 +3545,43 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455834</v>
+        <v>455956</v>
       </c>
       <c r="R25" t="n">
-        <v>7037660</v>
+        <v>7037592</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3604,7 +3613,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3614,12 +3623,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3646,10 +3655,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121598566</v>
+        <v>121598520</v>
       </c>
       <c r="B26" t="n">
-        <v>77546</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3662,37 +3671,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455834</v>
+        <v>455831</v>
       </c>
       <c r="R26" t="n">
-        <v>7037660</v>
+        <v>7037676</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3721,7 +3739,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3731,12 +3749,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (42 cm dbh, ca 150 år) i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3751,22 +3769,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121598525</v>
+        <v>121598566</v>
       </c>
       <c r="B27" t="n">
-        <v>78609</v>
+        <v>77553</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3779,43 +3797,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455852</v>
+        <v>455834</v>
       </c>
       <c r="R27" t="n">
-        <v>7037584</v>
+        <v>7037660</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3847,7 +3856,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3857,12 +3866,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal gran och björk</t>
+          <t>På bark på stam av levande gammal gran (42 cm dbh, ca 150 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3877,22 +3886,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121598835</v>
+        <v>121601448</v>
       </c>
       <c r="B28" t="n">
-        <v>78865</v>
+        <v>74713</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3901,25 +3910,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6459</v>
+        <v>492</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3929,10 +3938,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455963</v>
+        <v>455851</v>
       </c>
       <c r="R28" t="n">
-        <v>7037616</v>
+        <v>7037441</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3964,7 +3973,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3974,12 +3983,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gren på gammal gran</t>
+          <t>På ved på lyra vid basen av glasbjörk</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4006,10 +4015,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121601169</v>
+        <v>121601573</v>
       </c>
       <c r="B29" t="n">
-        <v>79719</v>
+        <v>74722</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4018,25 +4027,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4046,13 +4055,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455919</v>
+        <v>455805</v>
       </c>
       <c r="R29" t="n">
-        <v>7037597</v>
+        <v>7037437</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4081,7 +4090,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4091,12 +4100,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark på stam av levande rönn 23 cm dbh i gammal granskog</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4123,10 +4132,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121601174</v>
+        <v>121601743</v>
       </c>
       <c r="B30" t="n">
-        <v>74715</v>
+        <v>78616</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4139,39 +4148,43 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455933</v>
+        <v>455781</v>
       </c>
       <c r="R30" t="n">
-        <v>7037605</v>
+        <v>7037490</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4203,7 +4216,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4213,7 +4226,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
@@ -4233,22 +4246,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121601743</v>
+        <v>121598559</v>
       </c>
       <c r="B31" t="n">
-        <v>78609</v>
+        <v>79086</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4261,31 +4274,27 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1797</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4294,13 +4303,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455781</v>
+        <v>455834</v>
       </c>
       <c r="R31" t="n">
-        <v>7037490</v>
+        <v>7037660</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4329,7 +4338,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4339,12 +4348,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4371,10 +4380,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121601436</v>
+        <v>121598940</v>
       </c>
       <c r="B32" t="n">
-        <v>74699</v>
+        <v>79086</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4383,25 +4392,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6439</v>
+        <v>1797</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4411,10 +4420,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455851</v>
+        <v>455950</v>
       </c>
       <c r="R32" t="n">
-        <v>7037441</v>
+        <v>7037593</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4446,7 +4455,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4456,12 +4465,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av glasbjörk</t>
+          <t>På bark vid basen av gammal levande gran (55 cm dbh, ca 150 år gammal</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4488,10 +4497,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121598668</v>
+        <v>121601169</v>
       </c>
       <c r="B33" t="n">
-        <v>74527</v>
+        <v>79726</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4504,21 +4513,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6428</v>
+        <v>6462</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4528,13 +4537,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455858</v>
+        <v>455919</v>
       </c>
       <c r="R33" t="n">
-        <v>7037672</v>
+        <v>7037597</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4563,7 +4572,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4573,12 +4582,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal gran</t>
+          <t>På bark på stam av levande rönn 23 cm dbh i gammal granskog</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4605,10 +4614,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121601754</v>
+        <v>121598839</v>
       </c>
       <c r="B34" t="n">
-        <v>74715</v>
+        <v>74722</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4639,16 +4648,21 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455761</v>
+        <v>455930</v>
       </c>
       <c r="R34" t="n">
-        <v>7037494</v>
+        <v>7037619</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4680,7 +4694,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4690,12 +4704,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4710,22 +4719,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121598734</v>
+        <v>121601938</v>
       </c>
       <c r="B35" t="n">
-        <v>78609</v>
+        <v>79663</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4734,47 +4743,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>229748</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455911</v>
+        <v>455844</v>
       </c>
       <c r="R35" t="n">
-        <v>7037653</v>
+        <v>7037605</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4816,12 +4816,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande rönn (23 cm dbh)  i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4841,17 +4841,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121601941</v>
+        <v>121598734</v>
       </c>
       <c r="B36" t="n">
-        <v>79650</v>
+        <v>78616</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4860,38 +4860,47 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455844</v>
+        <v>455911</v>
       </c>
       <c r="R36" t="n">
-        <v>7037605</v>
+        <v>7037653</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4923,7 +4932,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4933,12 +4942,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4965,10 +4974,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121598940</v>
+        <v>121601299</v>
       </c>
       <c r="B37" t="n">
-        <v>79079</v>
+        <v>90728</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4981,21 +4990,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1797</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5005,10 +5014,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455950</v>
+        <v>455876</v>
       </c>
       <c r="R37" t="n">
-        <v>7037593</v>
+        <v>7037566</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5040,7 +5049,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5050,12 +5059,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran (55 cm dbh, ca 150 år gammal</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5082,10 +5091,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121599091</v>
+        <v>121601584</v>
       </c>
       <c r="B38" t="n">
-        <v>74715</v>
+        <v>78616</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5098,39 +5107,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455970</v>
+        <v>455813</v>
       </c>
       <c r="R38" t="n">
-        <v>7037654</v>
+        <v>7037433</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5162,7 +5166,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5172,12 +5176,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>Rikligt på glasbjörk i gammal granskog, längsta bål 40 cm</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5192,22 +5196,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121598839</v>
+        <v>121598835</v>
       </c>
       <c r="B39" t="n">
-        <v>74715</v>
+        <v>78872</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5216,43 +5220,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6459</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455930</v>
+        <v>455963</v>
       </c>
       <c r="R39" t="n">
-        <v>7037619</v>
+        <v>7037616</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5284,7 +5283,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5294,7 +5293,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På gren på gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5309,22 +5313,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121599010</v>
+        <v>121598525</v>
       </c>
       <c r="B40" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5356,7 +5360,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5366,17 +5370,17 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455998</v>
+        <v>455852</v>
       </c>
       <c r="R40" t="n">
-        <v>7037645</v>
+        <v>7037584</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5405,7 +5409,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5415,12 +5419,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal gran, mer än 200 bålar, granen 55 cm dbh.</t>
+          <t>På gammal gran och björk</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5435,22 +5439,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121598520</v>
+        <v>121599065</v>
       </c>
       <c r="B41" t="n">
-        <v>78609</v>
+        <v>79048</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5459,50 +5463,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1778</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Hepp</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455831</v>
+        <v>456010</v>
       </c>
       <c r="R41" t="n">
-        <v>7037676</v>
+        <v>7037665</v>
       </c>
       <c r="S41" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5531,7 +5526,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5541,12 +5536,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på rotben på gammal gran i brant</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5561,22 +5556,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin, August Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121599065</v>
+        <v>121599091</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>74722</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5585,38 +5580,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1778</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456010</v>
+        <v>455970</v>
       </c>
       <c r="R42" t="n">
-        <v>7037665</v>
+        <v>7037654</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På bark på rotben på gammal gran i brant</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5678,22 +5678,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121598771</v>
+        <v>121598649</v>
       </c>
       <c r="B43" t="n">
-        <v>78609</v>
+        <v>74720</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5702,50 +5702,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455915</v>
+        <v>455868</v>
       </c>
       <c r="R43" t="n">
-        <v>7037655</v>
+        <v>7037664</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5774,7 +5765,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5784,12 +5775,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På gammal/gamla granar</t>
+          <t>På bark i hålighet vid basen av grov gammal gran (50 cm dbh,  ca 150)</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5804,22 +5795,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121598974</v>
+        <v>121599010</v>
       </c>
       <c r="B44" t="n">
-        <v>90685</v>
+        <v>78616</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5828,41 +5819,50 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455990</v>
+        <v>455998</v>
       </c>
       <c r="R44" t="n">
-        <v>7037625</v>
+        <v>7037645</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gren på gammal gran</t>
+          <t>På gammal gran, mer än 200 bålar, granen 55 cm dbh.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5933,10 +5933,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121601695</v>
+        <v>121598771</v>
       </c>
       <c r="B45" t="n">
-        <v>79719</v>
+        <v>78616</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5945,38 +5945,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455760</v>
+        <v>455915</v>
       </c>
       <c r="R45" t="n">
-        <v>7037508</v>
+        <v>7037655</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6008,7 +6017,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6018,12 +6027,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På gammal/gamla granar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6038,22 +6047,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, August Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121601938</v>
+        <v>121598974</v>
       </c>
       <c r="B46" t="n">
-        <v>79656</v>
+        <v>90693</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6066,21 +6075,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229748</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6090,10 +6099,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455844</v>
+        <v>455990</v>
       </c>
       <c r="R46" t="n">
-        <v>7037605</v>
+        <v>7037625</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6125,7 +6134,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6135,12 +6144,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På bark på stam av levande rönn (23 cm dbh)  i gammal granskog</t>
+          <t>På gren på gammal gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6167,10 +6176,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121601573</v>
+        <v>121601695</v>
       </c>
       <c r="B47" t="n">
-        <v>74715</v>
+        <v>79726</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6179,25 +6188,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6207,10 +6216,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455805</v>
+        <v>455760</v>
       </c>
       <c r="R47" t="n">
-        <v>7037437</v>
+        <v>7037508</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6242,7 +6251,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6252,12 +6261,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6284,10 +6293,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121601908</v>
+        <v>121598668</v>
       </c>
       <c r="B48" t="n">
-        <v>78609</v>
+        <v>74534</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6296,47 +6305,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455848</v>
+        <v>455858</v>
       </c>
       <c r="R48" t="n">
-        <v>7037606</v>
+        <v>7037672</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gammal grov gran</t>
+          <t>På bark vid basen av gammal gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6410,10 +6410,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121601584</v>
+        <v>121601754</v>
       </c>
       <c r="B49" t="n">
-        <v>78609</v>
+        <v>74722</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6426,21 +6426,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6450,10 +6450,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455813</v>
+        <v>455761</v>
       </c>
       <c r="R49" t="n">
-        <v>7037433</v>
+        <v>7037494</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6485,7 +6485,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Rikligt på glasbjörk i gammal granskog, längsta bål 40 cm</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6527,10 +6527,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121598559</v>
+        <v>121598582</v>
       </c>
       <c r="B50" t="n">
-        <v>79079</v>
+        <v>74722</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6543,29 +6543,24 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1797</v>
+        <v>6440</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
@@ -6578,7 +6573,7 @@
         <v>7037660</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6622,7 +6617,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6649,10 +6644,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121601299</v>
+        <v>121601174</v>
       </c>
       <c r="B51" t="n">
-        <v>90720</v>
+        <v>74722</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6665,34 +6660,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455876</v>
+        <v>455933</v>
       </c>
       <c r="R51" t="n">
-        <v>7037566</v>
+        <v>7037605</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6754,19 +6754,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121601448</v>
+        <v>121601436</v>
       </c>
       <c r="B52" t="n">
         <v>74706</v>
@@ -6778,25 +6778,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>492</v>
+        <v>6439</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>

--- a/artfynd/A 28823-2024 artfynd.xlsx
+++ b/artfynd/A 28823-2024 artfynd.xlsx
@@ -3412,10 +3412,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121601941</v>
+        <v>121598798</v>
       </c>
       <c r="B24" t="n">
-        <v>79657</v>
+        <v>78616</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3424,38 +3424,47 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455844</v>
+        <v>455956</v>
       </c>
       <c r="R24" t="n">
-        <v>7037605</v>
+        <v>7037592</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3487,7 +3496,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3497,12 +3506,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3529,7 +3538,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121598798</v>
+        <v>121598520</v>
       </c>
       <c r="B25" t="n">
         <v>78616</v>
@@ -3564,7 +3573,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3574,17 +3583,17 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455956</v>
+        <v>455831</v>
       </c>
       <c r="R25" t="n">
-        <v>7037592</v>
+        <v>7037676</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3613,7 +3622,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3623,12 +3632,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3643,22 +3652,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121598520</v>
+        <v>121598566</v>
       </c>
       <c r="B26" t="n">
-        <v>78616</v>
+        <v>77553</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3671,46 +3680,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455831</v>
+        <v>455834</v>
       </c>
       <c r="R26" t="n">
-        <v>7037676</v>
+        <v>7037660</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3749,12 +3749,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran (42 cm dbh, ca 150 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3769,22 +3769,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin, August Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121598566</v>
+        <v>121601941</v>
       </c>
       <c r="B27" t="n">
-        <v>77553</v>
+        <v>79657</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3793,25 +3793,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228579</v>
+        <v>229497</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3821,10 +3821,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455834</v>
+        <v>455844</v>
       </c>
       <c r="R27" t="n">
-        <v>7037660</v>
+        <v>7037605</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3866,12 +3866,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (42 cm dbh, ca 150 år) i gammal granskog</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -5325,10 +5325,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121598525</v>
+        <v>121599091</v>
       </c>
       <c r="B40" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5341,31 +5341,27 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5374,10 +5370,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455852</v>
+        <v>455970</v>
       </c>
       <c r="R40" t="n">
-        <v>7037584</v>
+        <v>7037654</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5409,7 +5405,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5419,12 +5415,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal gran och björk</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5439,12 +5435,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5568,10 +5564,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121599091</v>
+        <v>121598525</v>
       </c>
       <c r="B42" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5584,27 +5580,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455970</v>
+        <v>455852</v>
       </c>
       <c r="R42" t="n">
-        <v>7037654</v>
+        <v>7037584</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran och björk</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5678,12 +5678,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 28823-2024 artfynd.xlsx
+++ b/artfynd/A 28823-2024 artfynd.xlsx
@@ -5325,10 +5325,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121599091</v>
+        <v>121598525</v>
       </c>
       <c r="B40" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5341,27 +5341,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5370,10 +5374,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455970</v>
+        <v>455852</v>
       </c>
       <c r="R40" t="n">
-        <v>7037654</v>
+        <v>7037584</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5405,7 +5409,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5415,12 +5419,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran och björk</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5435,12 +5439,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5564,10 +5568,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121598525</v>
+        <v>121599091</v>
       </c>
       <c r="B42" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5580,31 +5584,27 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5613,10 +5613,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455852</v>
+        <v>455970</v>
       </c>
       <c r="R42" t="n">
-        <v>7037584</v>
+        <v>7037654</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5648,7 +5648,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5658,12 +5658,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gammal gran och björk</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5678,12 +5678,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>

--- a/artfynd/A 28823-2024 artfynd.xlsx
+++ b/artfynd/A 28823-2024 artfynd.xlsx
@@ -3160,10 +3160,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121601436</v>
+        <v>121601169</v>
       </c>
       <c r="B22" t="n">
-        <v>74706</v>
+        <v>79726</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3176,21 +3176,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6439</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455851</v>
+        <v>455919</v>
       </c>
       <c r="R22" t="n">
-        <v>7037441</v>
+        <v>7037597</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av glasbjörk</t>
+          <t>På bark på stam av levande rönn 23 cm dbh i gammal granskog</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3277,10 +3277,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121598566</v>
+        <v>121601695</v>
       </c>
       <c r="B23" t="n">
-        <v>77553</v>
+        <v>79726</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3289,25 +3289,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228579</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455834</v>
+        <v>455760</v>
       </c>
       <c r="R23" t="n">
-        <v>7037660</v>
+        <v>7037508</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (42 cm dbh, ca 150 år) i gammal granskog</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3394,7 +3394,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121601584</v>
+        <v>121598798</v>
       </c>
       <c r="B24" t="n">
         <v>78616</v>
@@ -3427,17 +3427,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455813</v>
+        <v>455956</v>
       </c>
       <c r="R24" t="n">
-        <v>7037433</v>
+        <v>7037592</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3469,7 +3478,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3479,12 +3488,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt på glasbjörk i gammal granskog, längsta bål 40 cm</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3511,10 +3520,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121601754</v>
+        <v>121598940</v>
       </c>
       <c r="B25" t="n">
-        <v>74722</v>
+        <v>79086</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3527,21 +3536,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>1797</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3551,10 +3560,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455761</v>
+        <v>455950</v>
       </c>
       <c r="R25" t="n">
-        <v>7037494</v>
+        <v>7037593</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3586,7 +3595,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3596,12 +3605,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På bark vid basen av gammal levande gran (55 cm dbh, ca 150 år gammal</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3628,10 +3637,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121601174</v>
+        <v>121601938</v>
       </c>
       <c r="B26" t="n">
-        <v>74722</v>
+        <v>79663</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3640,40 +3649,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6440</v>
+        <v>229748</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455933</v>
+        <v>455844</v>
       </c>
       <c r="R26" t="n">
         <v>7037605</v>
@@ -3708,7 +3712,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3718,12 +3722,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande rönn (23 cm dbh)  i gammal granskog</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3738,19 +3742,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121599010</v>
+        <v>121601908</v>
       </c>
       <c r="B27" t="n">
         <v>78616</v>
@@ -3785,7 +3789,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3799,13 +3803,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455998</v>
+        <v>455848</v>
       </c>
       <c r="R27" t="n">
-        <v>7037645</v>
+        <v>7037606</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3834,7 +3838,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3844,12 +3848,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På gammal gran, mer än 200 bålar, granen 55 cm dbh.</t>
+          <t>På gammal grov gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3876,7 +3880,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121599091</v>
+        <v>121601754</v>
       </c>
       <c r="B28" t="n">
         <v>74722</v>
@@ -3910,21 +3914,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455970</v>
+        <v>455761</v>
       </c>
       <c r="R28" t="n">
-        <v>7037654</v>
+        <v>7037494</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3956,7 +3955,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3966,12 +3965,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3986,22 +3985,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121598649</v>
+        <v>121598559</v>
       </c>
       <c r="B29" t="n">
-        <v>74720</v>
+        <v>79086</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4010,38 +4009,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6486</v>
+        <v>1797</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455868</v>
+        <v>455834</v>
       </c>
       <c r="R29" t="n">
-        <v>7037664</v>
+        <v>7037660</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4073,7 +4077,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4083,12 +4087,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av grov gammal gran (50 cm dbh,  ca 150)</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4115,10 +4119,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121601743</v>
+        <v>121598566</v>
       </c>
       <c r="B30" t="n">
-        <v>78616</v>
+        <v>77553</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4131,43 +4135,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455781</v>
+        <v>455834</v>
       </c>
       <c r="R30" t="n">
-        <v>7037490</v>
+        <v>7037660</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4199,7 +4194,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4209,12 +4204,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran (42 cm dbh, ca 150 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4241,10 +4236,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121601938</v>
+        <v>121598525</v>
       </c>
       <c r="B31" t="n">
-        <v>79663</v>
+        <v>78616</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4253,38 +4248,47 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455844</v>
+        <v>455852</v>
       </c>
       <c r="R31" t="n">
-        <v>7037605</v>
+        <v>7037584</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4316,7 +4320,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4326,12 +4330,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På bark på stam av levande rönn (23 cm dbh)  i gammal granskog</t>
+          <t>På gammal gran och björk</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4346,22 +4350,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121598559</v>
+        <v>121601573</v>
       </c>
       <c r="B32" t="n">
-        <v>79086</v>
+        <v>74722</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4374,42 +4378,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1797</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455834</v>
+        <v>455805</v>
       </c>
       <c r="R32" t="n">
-        <v>7037660</v>
+        <v>7037437</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4438,7 +4437,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4448,12 +4447,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4480,10 +4479,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121598734</v>
+        <v>121598668</v>
       </c>
       <c r="B33" t="n">
-        <v>78616</v>
+        <v>74534</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4492,47 +4491,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455911</v>
+        <v>455858</v>
       </c>
       <c r="R33" t="n">
-        <v>7037653</v>
+        <v>7037672</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4564,7 +4554,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4574,12 +4564,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark vid basen av gammal gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4606,7 +4596,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121598771</v>
+        <v>121601743</v>
       </c>
       <c r="B34" t="n">
         <v>78616</v>
@@ -4651,14 +4641,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455915</v>
+        <v>455781</v>
       </c>
       <c r="R34" t="n">
-        <v>7037655</v>
+        <v>7037490</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4690,7 +4680,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4700,12 +4690,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal/gamla granar</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4720,22 +4710,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, August Nordin, Ludvig Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121601299</v>
+        <v>121601174</v>
       </c>
       <c r="B35" t="n">
-        <v>90728</v>
+        <v>74722</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4748,34 +4738,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455876</v>
+        <v>455933</v>
       </c>
       <c r="R35" t="n">
-        <v>7037566</v>
+        <v>7037605</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4807,7 +4802,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4817,12 +4812,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4837,22 +4832,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121601448</v>
+        <v>121601941</v>
       </c>
       <c r="B36" t="n">
-        <v>74713</v>
+        <v>79657</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4861,25 +4856,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>492</v>
+        <v>229497</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4889,10 +4884,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455851</v>
+        <v>455844</v>
       </c>
       <c r="R36" t="n">
-        <v>7037441</v>
+        <v>7037605</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4924,7 +4919,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4934,12 +4929,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av glasbjörk</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4966,10 +4961,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121598520</v>
+        <v>121601299</v>
       </c>
       <c r="B37" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4982,46 +4977,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455831</v>
+        <v>455876</v>
       </c>
       <c r="R37" t="n">
-        <v>7037676</v>
+        <v>7037566</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5050,7 +5036,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5060,12 +5046,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5080,22 +5066,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin, August Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121599065</v>
+        <v>121598520</v>
       </c>
       <c r="B38" t="n">
-        <v>79048</v>
+        <v>78616</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5104,41 +5090,50 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1778</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Hepp</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>456010</v>
+        <v>455831</v>
       </c>
       <c r="R38" t="n">
-        <v>7037665</v>
+        <v>7037676</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5167,7 +5162,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5177,12 +5172,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På bark på rotben på gammal gran i brant</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5197,22 +5192,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121598582</v>
+        <v>121601528</v>
       </c>
       <c r="B39" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5225,34 +5220,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455834</v>
+        <v>455821</v>
       </c>
       <c r="R39" t="n">
-        <v>7037660</v>
+        <v>7037413</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5284,7 +5288,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5294,12 +5298,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>Rikligt på gamla granar</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5326,10 +5330,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121598525</v>
+        <v>121601448</v>
       </c>
       <c r="B40" t="n">
-        <v>78616</v>
+        <v>74713</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5338,47 +5342,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>492</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455852</v>
+        <v>455851</v>
       </c>
       <c r="R40" t="n">
-        <v>7037584</v>
+        <v>7037441</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5410,7 +5405,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5420,12 +5415,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal gran och björk</t>
+          <t>På ved på lyra vid basen av glasbjörk</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5440,19 +5435,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121598798</v>
+        <v>121598734</v>
       </c>
       <c r="B41" t="n">
         <v>78616</v>
@@ -5501,10 +5496,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455956</v>
+        <v>455911</v>
       </c>
       <c r="R41" t="n">
-        <v>7037592</v>
+        <v>7037653</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5536,7 +5531,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5546,12 +5541,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5571,17 +5566,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121598835</v>
+        <v>121599065</v>
       </c>
       <c r="B42" t="n">
-        <v>78872</v>
+        <v>79048</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5590,25 +5585,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6459</v>
+        <v>1778</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5618,10 +5613,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>455963</v>
+        <v>456010</v>
       </c>
       <c r="R42" t="n">
-        <v>7037616</v>
+        <v>7037665</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5653,7 +5648,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5663,12 +5658,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gren på gammal gran</t>
+          <t>På bark på rotben på gammal gran i brant</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5688,17 +5683,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Ludvig Nordin, August Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121601573</v>
+        <v>121601584</v>
       </c>
       <c r="B43" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5711,21 +5706,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5735,10 +5730,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455805</v>
+        <v>455813</v>
       </c>
       <c r="R43" t="n">
-        <v>7037437</v>
+        <v>7037433</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5770,7 +5765,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5780,12 +5775,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>Rikligt på glasbjörk i gammal granskog, längsta bål 40 cm</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5812,10 +5807,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121598974</v>
+        <v>121598582</v>
       </c>
       <c r="B44" t="n">
-        <v>90693</v>
+        <v>74722</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5824,25 +5819,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6440</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5852,10 +5847,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455990</v>
+        <v>455834</v>
       </c>
       <c r="R44" t="n">
-        <v>7037625</v>
+        <v>7037660</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5887,7 +5882,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5897,12 +5892,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gren på gammal gran</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5929,10 +5924,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121598668</v>
+        <v>121598771</v>
       </c>
       <c r="B45" t="n">
-        <v>74534</v>
+        <v>78616</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5941,38 +5936,47 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455858</v>
+        <v>455915</v>
       </c>
       <c r="R45" t="n">
-        <v>7037672</v>
+        <v>7037655</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6004,7 +6008,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6014,12 +6018,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal gran</t>
+          <t>På gammal/gamla granar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6034,22 +6038,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, August Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121601908</v>
+        <v>121598974</v>
       </c>
       <c r="B46" t="n">
-        <v>78616</v>
+        <v>90693</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6058,47 +6062,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455848</v>
+        <v>455990</v>
       </c>
       <c r="R46" t="n">
-        <v>7037606</v>
+        <v>7037625</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6130,7 +6125,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6140,12 +6135,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gammal grov gran</t>
+          <t>På gren på gammal gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6172,10 +6167,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121598940</v>
+        <v>121599010</v>
       </c>
       <c r="B47" t="n">
-        <v>79086</v>
+        <v>78616</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6188,37 +6183,46 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1797</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455950</v>
+        <v>455998</v>
       </c>
       <c r="R47" t="n">
-        <v>7037593</v>
+        <v>7037645</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6247,7 +6251,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6257,12 +6261,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran (55 cm dbh, ca 150 år gammal</t>
+          <t>På gammal gran, mer än 200 bålar, granen 55 cm dbh.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6289,10 +6293,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121601528</v>
+        <v>121601436</v>
       </c>
       <c r="B48" t="n">
-        <v>78616</v>
+        <v>74706</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6301,47 +6305,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455821</v>
+        <v>455851</v>
       </c>
       <c r="R48" t="n">
-        <v>7037413</v>
+        <v>7037441</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6373,7 +6368,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6383,12 +6378,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar</t>
+          <t>På ved på lyra vid basen av glasbjörk</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6415,10 +6410,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121601695</v>
+        <v>121598839</v>
       </c>
       <c r="B49" t="n">
-        <v>79726</v>
+        <v>74722</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6427,38 +6422,43 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455760</v>
+        <v>455930</v>
       </c>
       <c r="R49" t="n">
-        <v>7037508</v>
+        <v>7037619</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6500,12 +6500,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6520,19 +6515,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121598839</v>
+        <v>121599091</v>
       </c>
       <c r="B50" t="n">
         <v>74722</v>
@@ -6577,10 +6572,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455930</v>
+        <v>455970</v>
       </c>
       <c r="R50" t="n">
-        <v>7037619</v>
+        <v>7037654</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6612,7 +6607,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6622,7 +6617,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6642,17 +6642,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ulrika Nordin, Fredrik Jonsson, Ludvig Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121601169</v>
+        <v>121598835</v>
       </c>
       <c r="B51" t="n">
-        <v>79726</v>
+        <v>78872</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6665,21 +6665,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>6459</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6689,13 +6689,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455919</v>
+        <v>455963</v>
       </c>
       <c r="R51" t="n">
-        <v>7037597</v>
+        <v>7037616</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På bark på stam av levande rönn 23 cm dbh i gammal granskog</t>
+          <t>På gren på gammal gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6766,10 +6766,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121601941</v>
+        <v>121598649</v>
       </c>
       <c r="B52" t="n">
-        <v>79657</v>
+        <v>74720</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6778,25 +6778,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229497</v>
+        <v>6486</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6806,13 +6806,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455844</v>
+        <v>455868</v>
       </c>
       <c r="R52" t="n">
-        <v>7037605</v>
+        <v>7037664</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>På bark i hålighet vid basen av grov gammal gran (50 cm dbh,  ca 150)</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 28823-2024 artfynd.xlsx
+++ b/artfynd/A 28823-2024 artfynd.xlsx
@@ -3160,10 +3160,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121601169</v>
+        <v>121598835</v>
       </c>
       <c r="B22" t="n">
-        <v>79726</v>
+        <v>78872</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3176,21 +3176,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>6459</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3200,13 +3200,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455919</v>
+        <v>455963</v>
       </c>
       <c r="R22" t="n">
-        <v>7037597</v>
+        <v>7037616</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande rönn 23 cm dbh i gammal granskog</t>
+          <t>På gren på gammal gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3277,10 +3277,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121601695</v>
+        <v>121599065</v>
       </c>
       <c r="B23" t="n">
-        <v>79726</v>
+        <v>79048</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3289,25 +3289,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>1778</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3317,10 +3317,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455760</v>
+        <v>456010</v>
       </c>
       <c r="R23" t="n">
-        <v>7037508</v>
+        <v>7037665</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>På bark på rotben på gammal gran i brant</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3394,7 +3394,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121598798</v>
+        <v>121598525</v>
       </c>
       <c r="B24" t="n">
         <v>78616</v>
@@ -3439,14 +3439,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455956</v>
+        <v>455852</v>
       </c>
       <c r="R24" t="n">
-        <v>7037592</v>
+        <v>7037584</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran och björk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3508,22 +3508,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121598940</v>
+        <v>121601174</v>
       </c>
       <c r="B25" t="n">
-        <v>79086</v>
+        <v>74722</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3536,34 +3536,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1797</v>
+        <v>6440</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455950</v>
+        <v>455933</v>
       </c>
       <c r="R25" t="n">
-        <v>7037593</v>
+        <v>7037605</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3595,7 +3600,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3605,12 +3610,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran (55 cm dbh, ca 150 år gammal</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3625,22 +3630,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121601938</v>
+        <v>121598520</v>
       </c>
       <c r="B26" t="n">
-        <v>79663</v>
+        <v>78616</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3649,41 +3654,50 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>229748</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>455844</v>
+        <v>455831</v>
       </c>
       <c r="R26" t="n">
-        <v>7037605</v>
+        <v>7037676</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3712,7 +3726,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3722,12 +3736,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På bark på stam av levande rönn (23 cm dbh)  i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3742,12 +3756,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3873,17 +3887,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121601754</v>
+        <v>121601941</v>
       </c>
       <c r="B28" t="n">
-        <v>74722</v>
+        <v>79657</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3892,25 +3906,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>229497</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3920,10 +3934,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455761</v>
+        <v>455844</v>
       </c>
       <c r="R28" t="n">
-        <v>7037494</v>
+        <v>7037605</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3955,7 +3969,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3965,12 +3979,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3997,10 +4011,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121598559</v>
+        <v>121598771</v>
       </c>
       <c r="B29" t="n">
-        <v>79086</v>
+        <v>78616</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -4013,42 +4027,46 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1797</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455834</v>
+        <v>455915</v>
       </c>
       <c r="R29" t="n">
-        <v>7037660</v>
+        <v>7037655</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4077,7 +4095,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4087,12 +4105,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
+          <t>På gammal/gamla granar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4107,22 +4125,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, August Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121598566</v>
+        <v>121598839</v>
       </c>
       <c r="B30" t="n">
-        <v>77553</v>
+        <v>74722</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4135,34 +4153,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455834</v>
+        <v>455930</v>
       </c>
       <c r="R30" t="n">
-        <v>7037660</v>
+        <v>7037619</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4194,7 +4217,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4204,12 +4227,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På bark på stam av levande gammal gran (42 cm dbh, ca 150 år) i gammal granskog</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4224,19 +4242,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121598525</v>
+        <v>121598734</v>
       </c>
       <c r="B31" t="n">
         <v>78616</v>
@@ -4281,14 +4299,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455852</v>
+        <v>455911</v>
       </c>
       <c r="R31" t="n">
-        <v>7037584</v>
+        <v>7037653</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4320,7 +4338,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4330,12 +4348,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal gran och björk</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4350,22 +4368,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121601573</v>
+        <v>121601584</v>
       </c>
       <c r="B32" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4378,21 +4396,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4402,10 +4420,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455805</v>
+        <v>455813</v>
       </c>
       <c r="R32" t="n">
-        <v>7037437</v>
+        <v>7037433</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4437,7 +4455,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4447,12 +4465,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>Rikligt på glasbjörk i gammal granskog, längsta bål 40 cm</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4479,10 +4497,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121598668</v>
+        <v>121601528</v>
       </c>
       <c r="B33" t="n">
-        <v>74534</v>
+        <v>78616</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4491,38 +4509,47 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6428</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455858</v>
+        <v>455821</v>
       </c>
       <c r="R33" t="n">
-        <v>7037672</v>
+        <v>7037413</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4554,7 +4581,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4564,12 +4591,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal gran</t>
+          <t>Rikligt på gamla granar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4596,10 +4623,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121601743</v>
+        <v>121598559</v>
       </c>
       <c r="B34" t="n">
-        <v>78616</v>
+        <v>79086</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4612,31 +4639,27 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1797</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -4645,13 +4668,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455781</v>
+        <v>455834</v>
       </c>
       <c r="R34" t="n">
-        <v>7037490</v>
+        <v>7037660</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4680,7 +4703,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4690,12 +4713,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4722,10 +4745,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121601174</v>
+        <v>121598798</v>
       </c>
       <c r="B35" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4738,39 +4761,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455933</v>
+        <v>455956</v>
       </c>
       <c r="R35" t="n">
-        <v>7037605</v>
+        <v>7037592</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4802,7 +4829,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4812,12 +4839,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4832,22 +4859,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121601941</v>
+        <v>121599010</v>
       </c>
       <c r="B36" t="n">
-        <v>79657</v>
+        <v>78616</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4856,41 +4883,50 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455844</v>
+        <v>455998</v>
       </c>
       <c r="R36" t="n">
-        <v>7037605</v>
+        <v>7037645</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4919,7 +4955,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4929,12 +4965,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>På gammal gran, mer än 200 bålar, granen 55 cm dbh.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4961,10 +4997,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121601299</v>
+        <v>121601938</v>
       </c>
       <c r="B37" t="n">
-        <v>90728</v>
+        <v>79663</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4973,25 +5009,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>229748</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -5001,10 +5037,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455876</v>
+        <v>455844</v>
       </c>
       <c r="R37" t="n">
-        <v>7037566</v>
+        <v>7037605</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5036,7 +5072,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5046,12 +5082,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På bark på stam av levande rönn (23 cm dbh)  i gammal granskog</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5078,10 +5114,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121598520</v>
+        <v>121601299</v>
       </c>
       <c r="B38" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5094,46 +5130,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455831</v>
+        <v>455876</v>
       </c>
       <c r="R38" t="n">
-        <v>7037676</v>
+        <v>7037566</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5162,7 +5189,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5172,12 +5199,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5192,22 +5219,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin, August Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121601528</v>
+        <v>121601754</v>
       </c>
       <c r="B39" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5220,43 +5247,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455821</v>
+        <v>455761</v>
       </c>
       <c r="R39" t="n">
-        <v>7037413</v>
+        <v>7037494</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5288,7 +5306,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5298,12 +5316,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5330,10 +5348,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121601448</v>
+        <v>121599091</v>
       </c>
       <c r="B40" t="n">
-        <v>74713</v>
+        <v>74722</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5342,38 +5360,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455851</v>
+        <v>455970</v>
       </c>
       <c r="R40" t="n">
-        <v>7037441</v>
+        <v>7037654</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5405,7 +5428,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5415,12 +5438,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av glasbjörk</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5435,22 +5458,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121598734</v>
+        <v>121601436</v>
       </c>
       <c r="B41" t="n">
-        <v>78616</v>
+        <v>74706</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5459,47 +5482,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455911</v>
+        <v>455851</v>
       </c>
       <c r="R41" t="n">
-        <v>7037653</v>
+        <v>7037441</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5531,7 +5545,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5541,12 +5555,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På ved på lyra vid basen av glasbjörk</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5573,10 +5587,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>121599065</v>
+        <v>121601448</v>
       </c>
       <c r="B42" t="n">
-        <v>79048</v>
+        <v>74713</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5589,21 +5603,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1778</v>
+        <v>492</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5613,10 +5627,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>456010</v>
+        <v>455851</v>
       </c>
       <c r="R42" t="n">
-        <v>7037665</v>
+        <v>7037441</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5648,7 +5662,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5658,12 +5672,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På bark på rotben på gammal gran i brant</t>
+          <t>På ved på lyra vid basen av glasbjörk</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5690,10 +5704,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121601584</v>
+        <v>121598582</v>
       </c>
       <c r="B43" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5706,21 +5720,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5730,10 +5744,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455813</v>
+        <v>455834</v>
       </c>
       <c r="R43" t="n">
-        <v>7037433</v>
+        <v>7037660</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5765,7 +5779,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5775,12 +5789,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt på glasbjörk i gammal granskog, längsta bål 40 cm</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5807,10 +5821,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121598582</v>
+        <v>121601743</v>
       </c>
       <c r="B44" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5823,34 +5837,43 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455834</v>
+        <v>455781</v>
       </c>
       <c r="R44" t="n">
-        <v>7037660</v>
+        <v>7037490</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5882,7 +5905,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5892,12 +5915,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5924,10 +5947,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121598771</v>
+        <v>121598974</v>
       </c>
       <c r="B45" t="n">
-        <v>78616</v>
+        <v>90693</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5936,47 +5959,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455915</v>
+        <v>455990</v>
       </c>
       <c r="R45" t="n">
-        <v>7037655</v>
+        <v>7037625</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6008,7 +6022,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6018,12 +6032,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På gammal/gamla granar</t>
+          <t>På gren på gammal gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6038,22 +6052,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121598974</v>
+        <v>121598566</v>
       </c>
       <c r="B46" t="n">
-        <v>90693</v>
+        <v>77553</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6062,25 +6076,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>228579</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -6090,10 +6104,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455990</v>
+        <v>455834</v>
       </c>
       <c r="R46" t="n">
-        <v>7037625</v>
+        <v>7037660</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6125,7 +6139,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6135,12 +6149,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gren på gammal gran</t>
+          <t>På bark på stam av levande gammal gran (42 cm dbh, ca 150 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6167,10 +6181,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121599010</v>
+        <v>121601169</v>
       </c>
       <c r="B47" t="n">
-        <v>78616</v>
+        <v>79726</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6179,47 +6193,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455998</v>
+        <v>455919</v>
       </c>
       <c r="R47" t="n">
-        <v>7037645</v>
+        <v>7037597</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -6251,7 +6256,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6261,12 +6266,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>På gammal gran, mer än 200 bålar, granen 55 cm dbh.</t>
+          <t>På bark på stam av levande rönn 23 cm dbh i gammal granskog</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6293,10 +6298,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121601436</v>
+        <v>121598649</v>
       </c>
       <c r="B48" t="n">
-        <v>74706</v>
+        <v>74720</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6305,25 +6310,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6439</v>
+        <v>6486</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6333,13 +6338,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455851</v>
+        <v>455868</v>
       </c>
       <c r="R48" t="n">
-        <v>7037441</v>
+        <v>7037664</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6368,7 +6373,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6378,12 +6383,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av glasbjörk</t>
+          <t>På bark i hålighet vid basen av grov gammal gran (50 cm dbh,  ca 150)</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6410,7 +6415,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121598839</v>
+        <v>121601573</v>
       </c>
       <c r="B49" t="n">
         <v>74722</v>
@@ -6444,21 +6449,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455930</v>
+        <v>455805</v>
       </c>
       <c r="R49" t="n">
-        <v>7037619</v>
+        <v>7037437</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6490,7 +6490,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6500,7 +6500,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6515,22 +6520,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121599091</v>
+        <v>121598940</v>
       </c>
       <c r="B50" t="n">
-        <v>74722</v>
+        <v>79086</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6543,39 +6548,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6440</v>
+        <v>1797</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455970</v>
+        <v>455950</v>
       </c>
       <c r="R50" t="n">
-        <v>7037654</v>
+        <v>7037593</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6617,12 +6617,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark vid basen av gammal levande gran (55 cm dbh, ca 150 år gammal</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6637,22 +6637,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121598835</v>
+        <v>121598668</v>
       </c>
       <c r="B51" t="n">
-        <v>78872</v>
+        <v>74534</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6665,21 +6665,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6459</v>
+        <v>6428</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6689,10 +6689,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>455963</v>
+        <v>455858</v>
       </c>
       <c r="R51" t="n">
-        <v>7037616</v>
+        <v>7037672</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På gren på gammal gran</t>
+          <t>På bark vid basen av gammal gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6766,10 +6766,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121598649</v>
+        <v>121601695</v>
       </c>
       <c r="B52" t="n">
-        <v>74720</v>
+        <v>79726</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6778,25 +6778,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6486</v>
+        <v>6462</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6806,13 +6806,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455868</v>
+        <v>455760</v>
       </c>
       <c r="R52" t="n">
-        <v>7037664</v>
+        <v>7037508</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av grov gammal gran (50 cm dbh,  ca 150)</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 28823-2024 artfynd.xlsx
+++ b/artfynd/A 28823-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY52"/>
+  <dimension ref="A1:AY53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118852291</v>
+        <v>121601448</v>
       </c>
       <c r="B2" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kläppberget Änge, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455859</v>
+        <v>455851</v>
       </c>
       <c r="R2" t="n">
-        <v>7037633</v>
+        <v>7037441</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På ved på lyra vid basen av glasbjörk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118852292</v>
+        <v>121601299</v>
       </c>
       <c r="B3" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kläppberget Änge, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455857</v>
+        <v>455876</v>
       </c>
       <c r="R3" t="n">
-        <v>7037619</v>
+        <v>7037566</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +852,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På gammal granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,27 +887,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118852293</v>
+        <v>120752464</v>
       </c>
       <c r="B4" t="n">
-        <v>90531</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kläppberget Änge, Jmt</t>
+          <t>MD4:835 97 Offerdal, Sweden, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455867</v>
+        <v>455804</v>
       </c>
       <c r="R4" t="n">
-        <v>7037570</v>
+        <v>7037509</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +964,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-01</t>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +994,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120752473</v>
+        <v>121107055</v>
       </c>
       <c r="B5" t="n">
-        <v>74704</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,37 +1017,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>MD1:Krokom, SE-JA, SE, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455908</v>
+        <v>455914</v>
       </c>
       <c r="R5" t="n">
-        <v>7037505</v>
+        <v>7037492</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1056,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1077,66 +1097,81 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>I gammal grandominerad skog med björk</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121107064</v>
+        <v>121107048</v>
       </c>
       <c r="B6" t="n">
-        <v>74711</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6486</v>
+        <v>1467</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, uppe på platån, drygt 2 km nordost om Änge, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>455767</v>
+        <v>455924</v>
       </c>
       <c r="R6" t="n">
-        <v>7037472</v>
+        <v>7037448</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1178,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,7 +1227,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1207,7 +1242,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>På gammal gran, i hålighet vid basen # Picea abies</t>
+          <t>På bark i hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1225,15 +1260,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121107060</v>
+        <v>121107057</v>
       </c>
       <c r="B7" t="n">
-        <v>78607</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1241,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1467</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1265,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>455889</v>
+        <v>455917</v>
       </c>
       <c r="R7" t="n">
-        <v>7037501</v>
+        <v>7037493</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1300,7 +1330,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1310,12 +1340,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:24</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1329,7 +1354,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1344,7 +1369,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1362,50 +1387,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121107052</v>
+        <v>121599065</v>
       </c>
       <c r="B8" t="n">
-        <v>105188</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79759</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221725</v>
+        <v>1778</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Fjällig knopplav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Biatora fallax</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Hepp</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>455910</v>
+        <v>456010</v>
       </c>
       <c r="R8" t="n">
-        <v>7037468</v>
+        <v>7037665</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,22 +1452,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-12-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-12-14</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På bark på rotben på gammal gran i brant</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1458,16 +1483,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>I gammal grandominerad skog med björk</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>På marken</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1477,60 +1492,60 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121107065</v>
+        <v>121598559</v>
       </c>
       <c r="B9" t="n">
-        <v>78607</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79798</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1797</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>455770</v>
+        <v>455834</v>
       </c>
       <c r="R9" t="n">
-        <v>7037463</v>
+        <v>7037660</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1554,27 +1569,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-12-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-12-14</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,26 +1600,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>På gamla granar # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1614,57 +1609,52 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Ulrika Nordin, Ludvig Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121107057</v>
+        <v>121598940</v>
       </c>
       <c r="B10" t="n">
-        <v>74718</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79798</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1467</v>
+        <v>1797</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Mjölig dropplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Cliostomum leprosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Räsänen) Holien &amp; Tønsberg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>455917</v>
+        <v>455950</v>
       </c>
       <c r="R10" t="n">
-        <v>7037493</v>
+        <v>7037593</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1691,22 +1681,27 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-12-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-12-14</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På bark vid basen av gammal levande gran (55 cm dbh, ca 150 år gammal</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,26 +1712,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>I gammal grandominerad skog med björk</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1746,44 +1721,39 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121107061</v>
+        <v>121107051</v>
       </c>
       <c r="B11" t="n">
-        <v>78607</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1793,10 +1763,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>455871</v>
+        <v>455911</v>
       </c>
       <c r="R11" t="n">
-        <v>7037484</v>
+        <v>7037465</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1828,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1838,12 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:21</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,22 +1822,12 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1890,37 +1845,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121107058</v>
+        <v>121107049</v>
       </c>
       <c r="B12" t="n">
-        <v>74713</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1930,10 +1880,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>455915</v>
+        <v>455920</v>
       </c>
       <c r="R12" t="n">
-        <v>7037497</v>
+        <v>7037457</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1965,7 +1915,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1975,7 +1925,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1989,22 +1939,12 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med tall och björk</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+          <t>I gammal grandominerad skog med björk</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>På gamla granar # Picea abies</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2022,15 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121107051</v>
+        <v>121598974</v>
       </c>
       <c r="B13" t="n">
-        <v>94500</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2038,34 +1973,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2809</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>455911</v>
+        <v>455990</v>
       </c>
       <c r="R13" t="n">
-        <v>7037465</v>
+        <v>7037625</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2092,22 +2027,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-12-14</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-12-14</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gren på gammal gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2118,16 +2058,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>I gammal grandominerad skog med björk</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>På marken</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2137,60 +2067,55 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121107049</v>
+        <v>120752465</v>
       </c>
       <c r="B14" t="n">
-        <v>91646</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>MD4:Krokom, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>455920</v>
+        <v>455887</v>
       </c>
       <c r="R14" t="n">
-        <v>7037457</v>
+        <v>7037494</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2219,7 +2144,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2229,7 +2154,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2240,76 +2165,66 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>I gammal grandominerad skog med björk</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>På marken</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121107055</v>
+        <v>121107059</v>
       </c>
       <c r="B15" t="n">
-        <v>82391</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>455914</v>
+        <v>455892</v>
       </c>
       <c r="R15" t="n">
-        <v>7037492</v>
+        <v>7037497</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2341,7 +2256,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2351,7 +2266,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2365,7 +2280,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -2380,7 +2295,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2398,15 +2313,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121107056</v>
+        <v>121107060</v>
       </c>
       <c r="B16" t="n">
-        <v>74711</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2414,21 +2324,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2438,10 +2348,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>455917</v>
+        <v>455889</v>
       </c>
       <c r="R16" t="n">
-        <v>7037493</v>
+        <v>7037501</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2473,7 +2383,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2483,7 +2393,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2497,7 +2412,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>I gammal grandominerad skog med björk</t>
+          <t>I gammal grandominerad skog med tall och björk</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -2512,7 +2427,7 @@
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+          <t>På gamla granar # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2530,19 +2445,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121107059</v>
+        <v>121107061</v>
       </c>
       <c r="B17" t="n">
-        <v>78607</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2564,21 +2474,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>455892</v>
+        <v>455871</v>
       </c>
       <c r="R17" t="n">
-        <v>7037497</v>
+        <v>7037484</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2610,7 +2515,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2620,7 +2525,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2670,16 +2580,11 @@
         <v>121107062</v>
       </c>
       <c r="B18" t="n">
-        <v>78607</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2799,19 +2704,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121107066</v>
+        <v>121107065</v>
       </c>
       <c r="B19" t="n">
-        <v>78607</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2839,10 +2739,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>455746</v>
+        <v>455770</v>
       </c>
       <c r="R19" t="n">
-        <v>7037456</v>
+        <v>7037463</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2874,7 +2774,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2884,12 +2784,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Mycket rikligt, draperade träd</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2936,15 +2836,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120752466</v>
+        <v>121107066</v>
       </c>
       <c r="B20" t="n">
-        <v>74711</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2952,37 +2847,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>MD3:Krokom, SE-JA, SE, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>455918</v>
+        <v>455746</v>
       </c>
       <c r="R20" t="n">
-        <v>7037497</v>
+        <v>7037456</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3011,7 +2906,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3021,7 +2916,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Mycket rikligt, draperade träd</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3032,35 +2932,50 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>I gammal grandominerad skog med tall och björk</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>På gamla granar # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120752465</v>
+        <v>121598520</v>
       </c>
       <c r="B21" t="n">
-        <v>78607</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -3081,20 +2996,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>MD4:Krokom, SE-JA, SE, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>455887</v>
+        <v>455831</v>
       </c>
       <c r="R21" t="n">
-        <v>7037494</v>
+        <v>7037676</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3118,22 +3042,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-12-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-12-14</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:32</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3148,70 +3077,69 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Mattias Dalkvist</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin, August Nordin</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>121598559</v>
+        <v>121598525</v>
       </c>
       <c r="B22" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1797</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>455834</v>
+        <v>455852</v>
       </c>
       <c r="R22" t="n">
-        <v>7037660</v>
+        <v>7037584</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3240,7 +3168,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3250,12 +3178,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (41 cm dbh, ca 150 år)</t>
+          <t>På gammal gran och björk</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3270,65 +3198,69 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>August Nordin</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121601169</v>
+        <v>121598734</v>
       </c>
       <c r="B23" t="n">
-        <v>79739</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>455919</v>
+        <v>455911</v>
       </c>
       <c r="R23" t="n">
-        <v>7037597</v>
+        <v>7037653</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3357,7 +3289,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3367,12 +3299,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På bark på stam av levande rönn 23 cm dbh i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3399,19 +3331,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121601584</v>
+        <v>121598771</v>
       </c>
       <c r="B24" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3432,17 +3359,26 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>455813</v>
+        <v>455915</v>
       </c>
       <c r="R24" t="n">
-        <v>7037433</v>
+        <v>7037655</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3474,7 +3410,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3484,12 +3420,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Rikligt på glasbjörk i gammal granskog, längsta bål 40 cm</t>
+          <t>På gammal/gamla granar</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3504,62 +3440,66 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, August Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121601754</v>
+        <v>121598798</v>
       </c>
       <c r="B25" t="n">
-        <v>74735</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>455761</v>
+        <v>455956</v>
       </c>
       <c r="R25" t="n">
-        <v>7037494</v>
+        <v>7037592</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3591,7 +3531,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3601,12 +3541,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På gammal gran i gammal granskog</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3636,16 +3576,11 @@
         <v>121599010</v>
       </c>
       <c r="B26" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3759,50 +3694,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121598582</v>
+        <v>121601528</v>
       </c>
       <c r="B27" t="n">
-        <v>74735</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>455834</v>
+        <v>455821</v>
       </c>
       <c r="R27" t="n">
-        <v>7037660</v>
+        <v>7037413</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3834,7 +3773,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3844,12 +3783,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>Rikligt på gamla granar</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3876,37 +3815,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121601436</v>
+        <v>121601584</v>
       </c>
       <c r="B28" t="n">
-        <v>74719</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3916,10 +3850,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>455851</v>
+        <v>455813</v>
       </c>
       <c r="R28" t="n">
-        <v>7037441</v>
+        <v>7037433</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3951,7 +3885,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3961,12 +3895,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av glasbjörk</t>
+          <t>Rikligt på glasbjörk i gammal granskog, längsta bål 40 cm</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3993,19 +3927,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121598734</v>
+        <v>121601743</v>
       </c>
       <c r="B29" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -4042,10 +3971,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>455911</v>
+        <v>455781</v>
       </c>
       <c r="R29" t="n">
-        <v>7037653</v>
+        <v>7037490</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4077,7 +4006,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4087,7 +4016,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
@@ -4119,50 +4048,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121601299</v>
+        <v>121601908</v>
       </c>
       <c r="B30" t="n">
-        <v>90742</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>455876</v>
+        <v>455848</v>
       </c>
       <c r="R30" t="n">
-        <v>7037566</v>
+        <v>7037606</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4194,7 +4127,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4204,12 +4137,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På gammal granlåga</t>
+          <t>På gammal grov gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4236,59 +4169,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121601528</v>
+        <v>121598668</v>
       </c>
       <c r="B31" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>455821</v>
+        <v>455858</v>
       </c>
       <c r="R31" t="n">
-        <v>7037413</v>
+        <v>7037672</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4320,7 +4239,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4330,12 +4249,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>12:59</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt på gamla granar</t>
+          <t>På bark vid basen av gammal gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4355,44 +4274,39 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121601573</v>
+        <v>121601436</v>
       </c>
       <c r="B32" t="n">
-        <v>74735</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6439</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4402,10 +4316,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>455805</v>
+        <v>455851</v>
       </c>
       <c r="R32" t="n">
-        <v>7037437</v>
+        <v>7037441</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4437,7 +4351,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4447,12 +4361,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran</t>
+          <t>På ved på lyra vid basen av glasbjörk</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4479,15 +4393,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121598525</v>
+        <v>120752473</v>
       </c>
       <c r="B33" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4495,46 +4404,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>MD1:Krokom, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>455852</v>
+        <v>455908</v>
       </c>
       <c r="R33" t="n">
-        <v>7037584</v>
+        <v>7037505</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4558,27 +4458,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-12-14</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-12-14</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:34</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gammal gran och björk</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4593,62 +4488,57 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>August Nordin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>August Nordin, Fredrik Jonsson, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121601695</v>
+        <v>121107058</v>
       </c>
       <c r="B34" t="n">
-        <v>79739</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>455760</v>
+        <v>455915</v>
       </c>
       <c r="R34" t="n">
-        <v>7037508</v>
+        <v>7037497</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4675,27 +4565,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-12-14</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-12-14</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:55</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4706,6 +4591,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>I gammal grandominerad skog med tall och björk</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>På gamla granar # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4715,44 +4620,39 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121598668</v>
+        <v>121598582</v>
       </c>
       <c r="B35" t="n">
-        <v>74547</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6428</v>
+        <v>6440</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4762,10 +4662,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>455858</v>
+        <v>455834</v>
       </c>
       <c r="R35" t="n">
-        <v>7037672</v>
+        <v>7037660</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4797,7 +4697,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4807,12 +4707,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:59</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal gran</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4832,22 +4732,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121599091</v>
+        <v>121598839</v>
       </c>
       <c r="B36" t="n">
-        <v>74735</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4884,10 +4779,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>455970</v>
+        <v>455930</v>
       </c>
       <c r="R36" t="n">
-        <v>7037654</v>
+        <v>7037619</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4919,7 +4814,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4929,12 +4824,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:47</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4954,57 +4844,57 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121601448</v>
+        <v>121598956</v>
       </c>
       <c r="B37" t="n">
-        <v>74726</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>455851</v>
+        <v>455998</v>
       </c>
       <c r="R37" t="n">
-        <v>7037441</v>
+        <v>7037586</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5036,7 +4926,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5046,12 +4936,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På ved på lyra vid basen av glasbjörk</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5066,65 +4956,65 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121598649</v>
+        <v>121599091</v>
       </c>
       <c r="B38" t="n">
-        <v>74733</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6486</v>
+        <v>6440</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>455868</v>
+        <v>455970</v>
       </c>
       <c r="R38" t="n">
-        <v>7037664</v>
+        <v>7037654</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5153,7 +5043,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5163,12 +5053,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På bark i hålighet vid basen av grov gammal gran (50 cm dbh,  ca 150)</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5183,27 +5073,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>121598798</v>
+        <v>121601174</v>
       </c>
       <c r="B39" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5211,43 +5096,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+          <t>Kläppberget, Kläppberget, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>455956</v>
+        <v>455933</v>
       </c>
       <c r="R39" t="n">
-        <v>7037592</v>
+        <v>7037605</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5279,7 +5160,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5289,12 +5170,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gammal gran i gammal granskog</t>
+          <t>På gammal gran</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5309,27 +5190,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Ludvig Nordin</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ludvig Nordin, Ulrika Nordin</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>121601908</v>
+        <v>121601573</v>
       </c>
       <c r="B40" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5337,43 +5213,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>455848</v>
+        <v>455805</v>
       </c>
       <c r="R40" t="n">
-        <v>7037606</v>
+        <v>7037437</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5405,7 +5272,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5415,12 +5282,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>På gammal grov gran</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5447,15 +5314,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>121601743</v>
+        <v>121601754</v>
       </c>
       <c r="B41" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5463,43 +5325,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>455781</v>
+        <v>455761</v>
       </c>
       <c r="R41" t="n">
-        <v>7037490</v>
+        <v>7037494</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5531,7 +5384,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5541,12 +5394,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På gammal gran</t>
+          <t>På bark på stam av levande gammal gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5576,12 +5429,7 @@
         <v>121598835</v>
       </c>
       <c r="B42" t="n">
-        <v>78885</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79583</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5690,15 +5538,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>121601938</v>
+        <v>121601169</v>
       </c>
       <c r="B43" t="n">
-        <v>79676</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5706,21 +5549,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229748</v>
+        <v>6462</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5730,13 +5573,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>455844</v>
+        <v>455919</v>
       </c>
       <c r="R43" t="n">
-        <v>7037605</v>
+        <v>7037597</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5765,7 +5608,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5775,12 +5618,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>På bark på stam av levande rönn (23 cm dbh)  i gammal granskog</t>
+          <t>På bark på stam av levande rönn 23 cm dbh i gammal granskog</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5807,15 +5650,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>121598974</v>
+        <v>121601695</v>
       </c>
       <c r="B44" t="n">
-        <v>90707</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5823,21 +5661,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>6462</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5847,10 +5685,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>455990</v>
+        <v>455760</v>
       </c>
       <c r="R44" t="n">
-        <v>7037625</v>
+        <v>7037508</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5882,7 +5720,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5892,12 +5730,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>På gren på gammal gran</t>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5924,62 +5762,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>121598771</v>
+        <v>120752466</v>
       </c>
       <c r="B45" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83305</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>MD3:Krokom, SE-JA, SE, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>455915</v>
+        <v>455918</v>
       </c>
       <c r="R45" t="n">
-        <v>7037655</v>
+        <v>7037497</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -6003,27 +5827,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-12-14</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-12-14</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:10</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På gammal/gamla granar</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6038,74 +5857,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, August Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>121598520</v>
+        <v>121107056</v>
       </c>
       <c r="B46" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83305</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>455831</v>
+        <v>455917</v>
       </c>
       <c r="R46" t="n">
-        <v>7037676</v>
+        <v>7037493</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6129,27 +5934,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-12-14</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:32</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-12-14</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:32</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6160,71 +5960,81 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>I gammal grandominerad skog med björk</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>I hålighet vid basen av gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin, August Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>121598839</v>
+        <v>121107064</v>
       </c>
       <c r="B47" t="n">
-        <v>74735</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83305</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6440</v>
+        <v>6486</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>455930</v>
+        <v>455767</v>
       </c>
       <c r="R47" t="n">
-        <v>7037619</v>
+        <v>7037472</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6251,22 +6061,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-12-14</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-12-14</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6277,53 +6087,68 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>I gammal grandominerad skog med tall och björk</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>På gammal gran, i hålighet vid basen # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Fredrik Jonsson, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>121601941</v>
+        <v>121598649</v>
       </c>
       <c r="B48" t="n">
-        <v>79670</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83305</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229497</v>
+        <v>6486</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6333,13 +6158,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>455844</v>
+        <v>455868</v>
       </c>
       <c r="R48" t="n">
-        <v>7037605</v>
+        <v>7037664</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6368,7 +6193,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6378,12 +6203,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:14</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På rönn</t>
+          <t>På bark i hålighet vid basen av grov gammal gran (50 cm dbh,  ca 150)</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6403,62 +6228,52 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>121601174</v>
+        <v>121107052</v>
       </c>
       <c r="B49" t="n">
-        <v>74735</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106229</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6440</v>
+        <v>221725</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kläppberget, Kläppberget, Jmt</t>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>455933</v>
+        <v>455910</v>
       </c>
       <c r="R49" t="n">
-        <v>7037605</v>
+        <v>7037468</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6485,27 +6300,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-12-14</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-12-14</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:22</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På gammal gran</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6516,31 +6326,36 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>I gammal grandominerad skog med björk</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>På marken</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Ludvig Nordin, Ulrika Nordin</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Ludvig Nordin, Mattias Dalkvist</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>121598940</v>
+        <v>121598566</v>
       </c>
       <c r="B50" t="n">
-        <v>79099</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6548,21 +6363,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1797</v>
+        <v>228579</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mjölig dropplav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cliostomum leprosum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Räsänen) Holien &amp; Tønsberg</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6572,10 +6387,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>455950</v>
+        <v>455834</v>
       </c>
       <c r="R50" t="n">
-        <v>7037593</v>
+        <v>7037660</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6607,7 +6422,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6617,12 +6432,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>På bark vid basen av gammal levande gran (55 cm dbh, ca 150 år gammal</t>
+          <t>På bark på stam av levande gammal gran (42 cm dbh, ca 150 år) i gammal granskog</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6642,44 +6457,39 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+          <t>Ulrika Nordin, Ludvig Nordin, August Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>121599065</v>
+        <v>121601941</v>
       </c>
       <c r="B51" t="n">
-        <v>79061</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80392</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1778</v>
+        <v>229497</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fjällig knopplav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Biatora fallax</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Hepp</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6689,10 +6499,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>456010</v>
+        <v>455844</v>
       </c>
       <c r="R51" t="n">
-        <v>7037665</v>
+        <v>7037605</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6724,7 +6534,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6734,12 +6544,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>På bark på rotben på gammal gran i brant</t>
+          <t>På rönn</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6766,37 +6576,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121598566</v>
+        <v>121601938</v>
       </c>
       <c r="B52" t="n">
-        <v>77566</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80398</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228579</v>
+        <v>229748</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gytterlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Protopannaria pezizoides</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6806,10 +6611,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>455834</v>
+        <v>455844</v>
       </c>
       <c r="R52" t="n">
-        <v>7037660</v>
+        <v>7037605</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6841,7 +6646,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6851,12 +6656,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>På bark på stam av levande gammal gran (42 cm dbh, ca 150 år) i gammal granskog</t>
+          <t>På bark på stam av levande rönn (23 cm dbh)  i gammal granskog</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6880,6 +6685,113 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>121601935</v>
+      </c>
+      <c r="B53" t="n">
+        <v>80344</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6331317</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Rostania pallida</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>A.Košuth. et al.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Kläppberget, platån, drygt 2 km NO Änge, Offerdal, fastighet Berge 1:10, Jmt</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>455844</v>
+      </c>
+      <c r="R53" t="n">
+        <v>7037605</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-12-14</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:14</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På bark på stam av levande rönn (15 cm dbh)</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, August Nordin, Ludvig Nordin, Ulrika Nordin</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
